--- a/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
@@ -1739,7 +1739,7 @@
         <v>276</v>
       </c>
       <c r="F47" t="n">
-        <v>59262</v>
+        <v>59260</v>
       </c>
       <c r="G47" t="n">
         <v>15251.7</v>
@@ -1938,10 +1938,10 @@
         <v>105888</v>
       </c>
       <c r="G54" t="n">
-        <v>2033.05</v>
+        <v>24396.6</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3391,7 +3391,7 @@
         <v>112</v>
       </c>
       <c r="F106" t="n">
-        <v>20485</v>
+        <v>20484</v>
       </c>
       <c r="G106" t="n">
         <v>20335.6</v>
@@ -3534,10 +3534,10 @@
         <v>54872</v>
       </c>
       <c r="G111" t="n">
-        <v>77604.2</v>
+        <v>74723.69</v>
       </c>
       <c r="H111" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112">
@@ -3559,7 +3559,7 @@
         <v>710</v>
       </c>
       <c r="F112" t="n">
-        <v>370904</v>
+        <v>370895</v>
       </c>
       <c r="G112" t="n">
         <v>14231.37</v>
@@ -3587,7 +3587,7 @@
         <v>131</v>
       </c>
       <c r="F113" t="n">
-        <v>38286</v>
+        <v>38285</v>
       </c>
       <c r="G113" t="n">
         <v>2033.05</v>
@@ -5715,7 +5715,7 @@
         <v>241</v>
       </c>
       <c r="F189" t="n">
-        <v>48484</v>
+        <v>48481</v>
       </c>
       <c r="G189" t="n">
         <v>3895.75</v>
@@ -5743,7 +5743,7 @@
         <v>500</v>
       </c>
       <c r="F190" t="n">
-        <v>55742</v>
+        <v>55737</v>
       </c>
       <c r="G190" t="n">
         <v>10627.14</v>
@@ -5827,7 +5827,7 @@
         <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -8179,7 +8179,7 @@
         <v>182</v>
       </c>
       <c r="F277" t="n">
-        <v>16035</v>
+        <v>16034</v>
       </c>
       <c r="G277" t="n">
         <v>10420.33</v>
@@ -8515,7 +8515,7 @@
         <v>172</v>
       </c>
       <c r="F289" t="n">
-        <v>46606</v>
+        <v>46605</v>
       </c>
       <c r="G289" t="n">
         <v>14211.03</v>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="F308" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>

--- a/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
@@ -464,40 +464,40 @@
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Campaign - 20/5/2026 16:32:01.948</t>
+          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2353.31</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>68973</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nex_HPC_SP_V-03_Comp_PT_B0DQCWRG3H</t>
+          <t>Nex_HnK_SP_Comp_PT_SC-01_B0CDPP45BM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -520,12 +520,12 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SC-01_B0CDPP45BM</t>
+          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -548,12 +548,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_Comp_PT_SM-01_B0D2LJSQXZ</t>
+          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -576,12 +576,12 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_HU-02_B0DVC8NYY2_HV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -604,22 +604,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>330.73</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1192</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,22 +632,22 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_Gen_HV_Exact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>330.73</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1192</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -660,12 +660,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_Gen_HV_Exact</t>
+          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -688,12 +688,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -716,12 +716,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nex_Hnk_SP_PT_ST-03_B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -744,12 +744,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-03_B0GN8WW6BC</t>
+          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -772,35 +772,35 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>5511.35</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>91388</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5464.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -809,26 +809,26 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5511.35</v>
+        <v>1435.47</v>
       </c>
       <c r="E14" t="n">
-        <v>356</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
-        <v>91388</v>
+        <v>4946</v>
       </c>
       <c r="G14" t="n">
-        <v>5464.4</v>
+        <v>5083.9</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1435.47</v>
+        <v>2620.63</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>202</v>
       </c>
       <c r="F15" t="n">
-        <v>4946</v>
+        <v>7286</v>
       </c>
       <c r="G15" t="n">
-        <v>5083.9</v>
+        <v>3812.71</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -856,7 +856,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,54 +865,54 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2620.63</v>
+        <v>4190.45</v>
       </c>
       <c r="E16" t="n">
-        <v>202</v>
+        <v>242</v>
       </c>
       <c r="F16" t="n">
-        <v>7286</v>
+        <v>19523</v>
       </c>
       <c r="G16" t="n">
-        <v>3812.71</v>
+        <v>4235.59</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4190.45</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>19523</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4235.59</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -921,44 +921,44 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792.71</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6875</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>792.71</v>
+        <v>223.97</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>6875</v>
+        <v>5448</v>
       </c>
       <c r="G19" t="n">
-        <v>1694.07</v>
+        <v>846.61</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -968,7 +968,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -977,13 +977,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>223.97</v>
+        <v>427.55</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F20" t="n">
-        <v>5448</v>
+        <v>7241</v>
       </c>
       <c r="G20" t="n">
         <v>846.61</v>
@@ -996,50 +996,50 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
+          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>427.55</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>7241</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>846.61</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>61.37</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2988</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1061,82 +1061,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61.37</v>
+        <v>1493.69</v>
       </c>
       <c r="E23" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="F23" t="n">
-        <v>2988</v>
+        <v>5428</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1694.06</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1493.69</v>
+        <v>1252.29</v>
       </c>
       <c r="E24" t="n">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="F24" t="n">
-        <v>5428</v>
+        <v>31833</v>
       </c>
       <c r="G24" t="n">
-        <v>1694.06</v>
+        <v>2989.83</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1252.29</v>
+        <v>2810.94</v>
       </c>
       <c r="E25" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="F25" t="n">
-        <v>31833</v>
+        <v>10674</v>
       </c>
       <c r="G25" t="n">
-        <v>2989.83</v>
+        <v>11522.04</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1145,26 +1145,26 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2810.94</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>10674</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>11522.04</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner- KT - Com - Exact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>247.53</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>4504</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner- KT - Com - Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>247.53</v>
+        <v>2015.67</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>230</v>
       </c>
       <c r="F28" t="n">
-        <v>4504</v>
+        <v>25586</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1229,13 +1229,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2015.67</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>25587</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,26 +1257,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1612.91</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5718</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,26 +1285,26 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1612.91</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1332,7 +1332,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1341,54 +1341,54 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>162.75</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4936</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>5761.02</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>162.75</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>4936</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>5761.02</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>317.29</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>10443</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,68 +1416,68 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>317.29</v>
+        <v>4226.45</v>
       </c>
       <c r="E36" t="n">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="F36" t="n">
-        <v>10443</v>
+        <v>21140</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>14280</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4226.45</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>21140</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>14280</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1500,35 +1500,35 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>2390.65</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>34488</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>10371.18</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,26 +1537,26 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2390.65</v>
+        <v>1204.67</v>
       </c>
       <c r="E40" t="n">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="F40" t="n">
-        <v>34489</v>
+        <v>4261</v>
       </c>
       <c r="G40" t="n">
-        <v>10371.18</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1204.67</v>
+        <v>1433.95</v>
       </c>
       <c r="E41" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F41" t="n">
-        <v>4261</v>
+        <v>10185</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,7 +1584,7 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1593,13 +1593,13 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1433.95</v>
+        <v>2440.26</v>
       </c>
       <c r="E42" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>10185</v>
+        <v>1543</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1621,13 +1621,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2440.26</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1543</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1640,12 +1640,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev - B0DQCWRG3H -  Ionic 3 in 1 Hot Air Brush - SP - AT - 00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1668,12 +1668,12 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev - B0DQCWRG3H -  Ionic 3 in 1 Hot Air Brush - SP - AT - 00</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1696,63 +1696,63 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>3636.03</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>59260</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3636.03</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>59260</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>15251.7</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1056.81</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>25331</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1789,26 +1789,26 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1056.81</v>
+        <v>1380.68</v>
       </c>
       <c r="E49" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="F49" t="n">
-        <v>25331</v>
+        <v>3433</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>7752.539999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1817,26 +1817,26 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1380.68</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>3433</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>7752.539999999999</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1864,7 +1864,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1873,54 +1873,54 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>15787.19</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>839</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>111940</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>42105.92</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15787.19</v>
+        <v>3093.65</v>
       </c>
       <c r="E53" t="n">
-        <v>839</v>
+        <v>219</v>
       </c>
       <c r="F53" t="n">
-        <v>111945</v>
+        <v>105888</v>
       </c>
       <c r="G53" t="n">
-        <v>42105.92</v>
+        <v>24396.6</v>
       </c>
       <c r="H53" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1929,26 +1929,26 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3093.65</v>
+        <v>3004.94</v>
       </c>
       <c r="E54" t="n">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="F54" t="n">
-        <v>105888</v>
+        <v>31068</v>
       </c>
       <c r="G54" t="n">
-        <v>24396.6</v>
+        <v>2033.05</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1957,41 +1957,41 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3004.94</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>31068</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>2033.05</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>63.48</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -2004,22 +2004,22 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>63.48</v>
+        <v>5.87</v>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>745</v>
+        <v>103</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2032,63 +2032,63 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5.87</v>
+        <v>17474.69</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>701</v>
       </c>
       <c r="F58" t="n">
-        <v>103</v>
+        <v>94195</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>53120.33</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>17474.69</v>
+        <v>2882.58</v>
       </c>
       <c r="E59" t="n">
-        <v>701</v>
+        <v>158</v>
       </c>
       <c r="F59" t="n">
-        <v>94195</v>
+        <v>10312</v>
       </c>
       <c r="G59" t="n">
-        <v>53120.33</v>
+        <v>7878.8</v>
       </c>
       <c r="H59" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2097,26 +2097,26 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2882.58</v>
+        <v>1029.15</v>
       </c>
       <c r="E60" t="n">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="F60" t="n">
-        <v>10312</v>
+        <v>3361</v>
       </c>
       <c r="G60" t="n">
-        <v>7878.8</v>
+        <v>2541.53</v>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2125,69 +2125,69 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1029.15</v>
+        <v>1476.6</v>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>108</v>
       </c>
       <c r="F61" t="n">
-        <v>3361</v>
+        <v>3383</v>
       </c>
       <c r="G61" t="n">
-        <v>2541.53</v>
+        <v>5083.05</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1476.6</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>3383</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>5083.05</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
+          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>667.92</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1945</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2200,22 +2200,22 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
+          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>667.92</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1945</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2228,63 +2228,63 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>1883.16</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3324</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1883.16</v>
+        <v>4829.18</v>
       </c>
       <c r="E66" t="n">
-        <v>69</v>
+        <v>436</v>
       </c>
       <c r="F66" t="n">
-        <v>3324</v>
+        <v>38085</v>
       </c>
       <c r="G66" t="n">
-        <v>5083.9</v>
+        <v>14105.93</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2293,69 +2293,69 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4829.18</v>
+        <v>3041.94</v>
       </c>
       <c r="E67" t="n">
-        <v>436</v>
+        <v>224</v>
       </c>
       <c r="F67" t="n">
-        <v>38086</v>
+        <v>5203</v>
       </c>
       <c r="G67" t="n">
-        <v>14105.93</v>
+        <v>14233.05</v>
       </c>
       <c r="H67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3041.94</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>5203</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>11267.8</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>542.5599999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>8832</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,22 +2368,22 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>542.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>8832</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2424,12 +2424,12 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2480,22 +2480,22 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>15.72</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>937</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2508,35 +2508,35 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15.72</v>
+        <v>1526.85</v>
       </c>
       <c r="E75" t="n">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="F75" t="n">
-        <v>937</v>
+        <v>6530</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>14996.61</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2545,54 +2545,54 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1526.85</v>
+        <v>4739.67</v>
       </c>
       <c r="E76" t="n">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F76" t="n">
-        <v>6530</v>
+        <v>24739</v>
       </c>
       <c r="G76" t="n">
-        <v>14996.61</v>
+        <v>3812.71</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4739.67</v>
+        <v>1077.15</v>
       </c>
       <c r="E77" t="n">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="F77" t="n">
-        <v>24740</v>
+        <v>8672</v>
       </c>
       <c r="G77" t="n">
-        <v>3812.71</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1077.15</v>
+        <v>1342.38</v>
       </c>
       <c r="E78" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F78" t="n">
-        <v>8672</v>
+        <v>3292</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,7 +2620,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1342.38</v>
+        <v>1443.32</v>
       </c>
       <c r="E79" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F79" t="n">
-        <v>3292</v>
+        <v>12487</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,7 +2648,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1443.32</v>
+        <v>1961.47</v>
       </c>
       <c r="E80" t="n">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="F80" t="n">
-        <v>12487</v>
+        <v>8031</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2676,22 +2676,22 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1961.47</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>8031</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2732,12 +2732,12 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2760,12 +2760,12 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -2788,12 +2788,12 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -2816,7 +2816,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2844,35 +2844,35 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>763.83</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>9474</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1046.67</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2881,82 +2881,82 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>763.83</v>
+        <v>123.42</v>
       </c>
       <c r="E88" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="F88" t="n">
-        <v>9474</v>
+        <v>248</v>
       </c>
       <c r="G88" t="n">
-        <v>1046.67</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>123.42</v>
+        <v>1997.36</v>
       </c>
       <c r="E89" t="n">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F89" t="n">
-        <v>248</v>
+        <v>44910</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>2879.66</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1997.36</v>
+        <v>129.41</v>
       </c>
       <c r="E90" t="n">
-        <v>96</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>44910</v>
+        <v>902</v>
       </c>
       <c r="G90" t="n">
-        <v>2879.66</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2965,41 +2965,41 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>129.41</v>
+        <v>623.73</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>902</v>
+        <v>13371</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2856.19</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>623.73</v>
+        <v>246.15</v>
       </c>
       <c r="E92" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F92" t="n">
-        <v>13371</v>
+        <v>2097</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,7 +3012,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3021,44 +3021,44 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>246.15</v>
+        <v>430.81</v>
       </c>
       <c r="E93" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F93" t="n">
-        <v>2097</v>
+        <v>2380</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>2287.29</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>430.81</v>
+        <v>3251.47</v>
       </c>
       <c r="E94" t="n">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="F94" t="n">
-        <v>2380</v>
+        <v>26510</v>
       </c>
       <c r="G94" t="n">
-        <v>2287.29</v>
+        <v>2880.5</v>
       </c>
       <c r="H94" t="n">
         <v>1</v>
@@ -3068,7 +3068,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3077,41 +3077,41 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3251.47</v>
+        <v>616.8</v>
       </c>
       <c r="E95" t="n">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="F95" t="n">
-        <v>26510</v>
+        <v>810</v>
       </c>
       <c r="G95" t="n">
-        <v>2880.5</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>616.8</v>
+        <v>904.25</v>
       </c>
       <c r="E96" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F96" t="n">
-        <v>810</v>
+        <v>2207</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3133,44 +3133,44 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>904.25</v>
+        <v>705.3299999999999</v>
       </c>
       <c r="E97" t="n">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="F97" t="n">
-        <v>2207</v>
+        <v>12645</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>11613.34</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>705.3299999999999</v>
+        <v>3608.31</v>
       </c>
       <c r="E98" t="n">
-        <v>77</v>
+        <v>204</v>
       </c>
       <c r="F98" t="n">
-        <v>12645</v>
+        <v>34801</v>
       </c>
       <c r="G98" t="n">
-        <v>11613.34</v>
+        <v>27011.86</v>
       </c>
       <c r="H98" t="n">
         <v>8</v>
@@ -3180,7 +3180,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3189,26 +3189,26 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3608.31</v>
+        <v>2158.58</v>
       </c>
       <c r="E99" t="n">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="F99" t="n">
-        <v>34802</v>
+        <v>4285</v>
       </c>
       <c r="G99" t="n">
-        <v>27011.86</v>
+        <v>5083.9</v>
       </c>
       <c r="H99" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3217,26 +3217,26 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>2158.58</v>
+        <v>539.4400000000001</v>
       </c>
       <c r="E100" t="n">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="F100" t="n">
-        <v>4285</v>
+        <v>2391</v>
       </c>
       <c r="G100" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3245,44 +3245,44 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>539.4400000000001</v>
+        <v>3976.73</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="F101" t="n">
-        <v>2391</v>
+        <v>10083</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3976.73</v>
+        <v>1147.53</v>
       </c>
       <c r="E102" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F102" t="n">
-        <v>10083</v>
+        <v>18221</v>
       </c>
       <c r="G102" t="n">
-        <v>5083.9</v>
+        <v>1736.44</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -3292,7 +3292,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3301,13 +3301,13 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1147.53</v>
+        <v>2299.48</v>
       </c>
       <c r="E103" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
       <c r="F103" t="n">
-        <v>18221</v>
+        <v>39930</v>
       </c>
       <c r="G103" t="n">
         <v>1736.44</v>
@@ -3320,35 +3320,35 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>2299.48</v>
+        <v>1685.3</v>
       </c>
       <c r="E104" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="F104" t="n">
-        <v>39930</v>
+        <v>87579</v>
       </c>
       <c r="G104" t="n">
-        <v>1736.44</v>
+        <v>20335.6</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3357,13 +3357,13 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1685.3</v>
+        <v>1824.54</v>
       </c>
       <c r="E105" t="n">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="F105" t="n">
-        <v>87579</v>
+        <v>20484</v>
       </c>
       <c r="G105" t="n">
         <v>20335.6</v>
@@ -3376,7 +3376,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3385,54 +3385,54 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1824.54</v>
+        <v>484.76</v>
       </c>
       <c r="E106" t="n">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="F106" t="n">
-        <v>20484</v>
+        <v>2037</v>
       </c>
       <c r="G106" t="n">
-        <v>20335.6</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>484.76</v>
+        <v>4617.18</v>
       </c>
       <c r="E107" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F107" t="n">
-        <v>2037</v>
+        <v>18756</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>13894.06</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3441,26 +3441,26 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>4617.18</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>18756</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>10844.06</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3488,7 +3488,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3497,54 +3497,54 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>84</v>
+        <v>14794.85</v>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>854</v>
       </c>
       <c r="F110" t="n">
-        <v>956</v>
+        <v>54869</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>74723.69</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>14794.85</v>
+        <v>9195.870000000001</v>
       </c>
       <c r="E111" t="n">
-        <v>854</v>
+        <v>710</v>
       </c>
       <c r="F111" t="n">
-        <v>54872</v>
+        <v>370895</v>
       </c>
       <c r="G111" t="n">
-        <v>74723.69</v>
+        <v>14231.37</v>
       </c>
       <c r="H111" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3553,26 +3553,26 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>9195.870000000001</v>
+        <v>1010.91</v>
       </c>
       <c r="E112" t="n">
-        <v>710</v>
+        <v>131</v>
       </c>
       <c r="F112" t="n">
-        <v>370895</v>
+        <v>38284</v>
       </c>
       <c r="G112" t="n">
-        <v>14231.37</v>
+        <v>2033.05</v>
       </c>
       <c r="H112" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3581,41 +3581,41 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1010.91</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>38285</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>2033.05</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>193.91</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>2823</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,7 +3628,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3637,26 +3637,26 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>193.91</v>
+        <v>1468.22</v>
       </c>
       <c r="E115" t="n">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="F115" t="n">
-        <v>2824</v>
+        <v>23461</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>4320.34</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3665,47 +3665,47 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1468.22</v>
+        <v>497.69</v>
       </c>
       <c r="E116" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="F116" t="n">
-        <v>23461</v>
+        <v>5413</v>
       </c>
       <c r="G116" t="n">
-        <v>4320.34</v>
+        <v>1439.84</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>497.69</v>
+        <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>5413</v>
+        <v>15</v>
       </c>
       <c r="G117" t="n">
-        <v>1439.84</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
+        <v>46.22</v>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F118" t="n">
-        <v>15</v>
+        <v>4857</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,17 +3745,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>46.22</v>
+        <v>27.64</v>
       </c>
       <c r="E119" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" t="n">
-        <v>4857</v>
+        <v>1315</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3773,17 +3773,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>27.64</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>1315</v>
+        <v>126</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3801,17 +3801,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>31.07</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F121" t="n">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.07</v>
+        <v>6.85</v>
       </c>
       <c r="E122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F122" t="n">
-        <v>57</v>
+        <v>367</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3857,17 +3857,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="E123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>367</v>
+        <v>240</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3885,23 +3885,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>48.64</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F124" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -3913,23 +3913,23 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>48.64</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="G125" t="n">
-        <v>951.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>32.79</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F126" t="n">
-        <v>16</v>
+        <v>354</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3969,23 +3969,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>32.79</v>
+        <v>74.53999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F127" t="n">
-        <v>354</v>
+        <v>4277</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -3997,23 +3997,23 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>74.53999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="E128" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>4277</v>
+        <v>91</v>
       </c>
       <c r="G128" t="n">
-        <v>761.86</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4053,7 +4053,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4081,17 +4081,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>170</v>
+        <v>273</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4109,17 +4109,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.2</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E132" t="n">
         <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>273</v>
+        <v>699</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -4137,17 +4137,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>9.949999999999999</v>
+        <v>6.77</v>
       </c>
       <c r="E133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>699</v>
+        <v>146</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -4165,17 +4165,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>6.77</v>
+        <v>30.34</v>
       </c>
       <c r="E134" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F134" t="n">
-        <v>146</v>
+        <v>375</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>30.34</v>
+        <v>34.04</v>
       </c>
       <c r="E135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F135" t="n">
-        <v>375</v>
+        <v>143</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4221,23 +4221,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>34.04</v>
+        <v>58.04</v>
       </c>
       <c r="E136" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F136" t="n">
-        <v>143</v>
+        <v>1687</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>3465.26</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137">
@@ -4249,23 +4249,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>58.04</v>
+        <v>166.42</v>
       </c>
       <c r="E137" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F137" t="n">
-        <v>1687</v>
+        <v>2358</v>
       </c>
       <c r="G137" t="n">
-        <v>3465.26</v>
+        <v>1771.19</v>
       </c>
       <c r="H137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -4277,23 +4277,23 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>166.42</v>
+        <v>6.71</v>
       </c>
       <c r="E138" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>2358</v>
+        <v>6</v>
       </c>
       <c r="G138" t="n">
-        <v>1771.19</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>6.13</v>
+        <v>338.82</v>
       </c>
       <c r="E142" t="n">
+        <v>53</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6041</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1948.31</v>
+      </c>
+      <c r="H142" t="n">
         <v>1</v>
-      </c>
-      <c r="F142" t="n">
-        <v>35</v>
-      </c>
-      <c r="G142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -4417,23 +4417,23 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>338.82</v>
+        <v>112.75</v>
       </c>
       <c r="E143" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="F143" t="n">
-        <v>6041</v>
+        <v>2601</v>
       </c>
       <c r="G143" t="n">
-        <v>1948.31</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -4445,17 +4445,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>112.75</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>2601</v>
+        <v>103</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>13.56</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4529,17 +4529,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>13.56</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4557,17 +4557,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>53.49</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F148" t="n">
-        <v>78</v>
+        <v>600</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4585,17 +4585,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>53.49</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" t="n">
         <v>9</v>
-      </c>
-      <c r="F149" t="n">
-        <v>600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4613,17 +4613,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F150" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4641,17 +4641,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>39</v>
+        <v>174</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F152" t="n">
-        <v>174</v>
+        <v>357</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>60</v>
+        <v>35.57</v>
       </c>
       <c r="E153" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F153" t="n">
-        <v>357</v>
+        <v>2887</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4725,17 +4725,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>35.57</v>
+        <v>37.52</v>
       </c>
       <c r="E154" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F154" t="n">
-        <v>2887</v>
+        <v>3091</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4753,17 +4753,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>37.52</v>
+        <v>14.85</v>
       </c>
       <c r="E155" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F155" t="n">
-        <v>3091</v>
+        <v>543</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>14.85</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>543</v>
+        <v>134</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4809,17 +4809,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>134</v>
+        <v>447</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>2.33</v>
+        <v>8</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" t="n">
-        <v>447</v>
+        <v>138</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4865,17 +4865,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8</v>
+        <v>5.83</v>
       </c>
       <c r="E159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>138</v>
+        <v>66</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4893,17 +4893,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>66</v>
+        <v>1873</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4921,23 +4921,23 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>57.09999999999999</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F161" t="n">
-        <v>1873</v>
+        <v>7882</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>168.64</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -4949,23 +4949,23 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>57.09999999999999</v>
+        <v>6.119999999999999</v>
       </c>
       <c r="E162" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F162" t="n">
-        <v>7882</v>
+        <v>140</v>
       </c>
       <c r="G162" t="n">
-        <v>168.64</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -4977,17 +4977,17 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6.119999999999999</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>140</v>
+        <v>265</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -5005,17 +5005,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>6.68</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>265</v>
+        <v>405</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5033,17 +5033,17 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>405</v>
+        <v>286</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5061,17 +5061,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>17.05</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F166" t="n">
-        <v>286</v>
+        <v>92</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5089,23 +5089,23 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>17.05</v>
+        <v>46.89</v>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F167" t="n">
-        <v>92</v>
+        <v>2321</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>672.89</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -5117,20 +5117,20 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>46.89</v>
+        <v>173.45</v>
       </c>
       <c r="E168" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F168" t="n">
-        <v>2321</v>
+        <v>4765</v>
       </c>
       <c r="G168" t="n">
-        <v>672.89</v>
+        <v>13550</v>
       </c>
       <c r="H168" t="n">
         <v>2</v>
@@ -5140,28 +5140,28 @@
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>173.45</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>4765</v>
+        <v>83</v>
       </c>
       <c r="G169" t="n">
-        <v>13550</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="E170" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F170" t="n">
-        <v>83</v>
+        <v>1099</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>15.4</v>
+        <v>7.77</v>
       </c>
       <c r="E171" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F171" t="n">
-        <v>1099</v>
+        <v>829</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>7.77</v>
+        <v>10.5</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F172" t="n">
-        <v>829</v>
+        <v>603</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5257,17 +5257,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.5</v>
+        <v>35.81</v>
       </c>
       <c r="E173" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F173" t="n">
-        <v>603</v>
+        <v>8993</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5285,23 +5285,23 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>35.81</v>
+        <v>36.89</v>
       </c>
       <c r="E174" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F174" t="n">
-        <v>8993</v>
+        <v>2445</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -5313,23 +5313,23 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>36.89</v>
+        <v>26.59</v>
       </c>
       <c r="E175" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F175" t="n">
-        <v>2445</v>
+        <v>2091</v>
       </c>
       <c r="G175" t="n">
-        <v>677.12</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>26.59</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>2091</v>
+        <v>680</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>7.76</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>680</v>
+        <v>2303</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>7.76</v>
+        <v>3.65</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F178" t="n">
-        <v>2303</v>
+        <v>1347</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5425,23 +5425,23 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>3.65</v>
+        <v>27.8</v>
       </c>
       <c r="E179" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F179" t="n">
-        <v>1347</v>
+        <v>1568</v>
       </c>
       <c r="G179" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -5453,23 +5453,23 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>27.8</v>
+        <v>2.75</v>
       </c>
       <c r="E180" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F180" t="n">
-        <v>1568</v>
+        <v>12857</v>
       </c>
       <c r="G180" t="n">
-        <v>761.86</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -5481,17 +5481,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2.75</v>
+        <v>7.57</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F181" t="n">
-        <v>12857</v>
+        <v>732</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5509,17 +5509,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>7.57</v>
+        <v>12.04</v>
       </c>
       <c r="E182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F182" t="n">
-        <v>732</v>
+        <v>1024</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5537,17 +5537,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>12.04</v>
+        <v>60.86</v>
       </c>
       <c r="E183" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F183" t="n">
-        <v>1024</v>
+        <v>4687</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5565,17 +5565,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>60.86</v>
+        <v>10.33</v>
       </c>
       <c r="E184" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F184" t="n">
-        <v>4688</v>
+        <v>519</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5593,17 +5593,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>10.33</v>
+        <v>3.67</v>
       </c>
       <c r="E185" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>519</v>
+        <v>193</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>193</v>
+        <v>373</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5649,17 +5649,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>3.66</v>
+        <v>19.53</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F187" t="n">
-        <v>373</v>
+        <v>413</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5677,23 +5677,23 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>19.53</v>
+        <v>726.33</v>
       </c>
       <c r="E188" t="n">
-        <v>6</v>
+        <v>241</v>
       </c>
       <c r="F188" t="n">
-        <v>413</v>
+        <v>48480</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -5705,23 +5705,23 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>726.33</v>
+        <v>1532.04</v>
       </c>
       <c r="E189" t="n">
-        <v>241</v>
+        <v>500</v>
       </c>
       <c r="F189" t="n">
-        <v>48481</v>
+        <v>55730</v>
       </c>
       <c r="G189" t="n">
-        <v>3895.75</v>
+        <v>10627.14</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190">
@@ -5733,23 +5733,23 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1532.04</v>
+        <v>4.29</v>
       </c>
       <c r="E190" t="n">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="F190" t="n">
-        <v>55737</v>
+        <v>848</v>
       </c>
       <c r="G190" t="n">
-        <v>10627.14</v>
+        <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -5761,17 +5761,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>4.29</v>
+        <v>53.5</v>
       </c>
       <c r="E191" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="F191" t="n">
-        <v>848</v>
+        <v>4186</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5789,17 +5789,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>53.5</v>
+        <v>4.12</v>
       </c>
       <c r="E192" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="F192" t="n">
-        <v>4186</v>
+        <v>1270</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5817,23 +5817,23 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>4.12</v>
+        <v>117.38</v>
       </c>
       <c r="E193" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="F193" t="n">
-        <v>1270</v>
+        <v>14317</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>3048.3</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
@@ -5845,23 +5845,23 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>119.92</v>
+        <v>20.74</v>
       </c>
       <c r="E194" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="F194" t="n">
-        <v>14318</v>
+        <v>3188</v>
       </c>
       <c r="G194" t="n">
-        <v>3048.3</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>20.74</v>
+        <v>49.59</v>
       </c>
       <c r="E195" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F195" t="n">
-        <v>3188</v>
+        <v>1761</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>49.59</v>
+        <v>2.3</v>
       </c>
       <c r="E196" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>1761</v>
+        <v>152</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5929,17 +5929,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5957,17 +5957,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0</v>
+        <v>7.34</v>
       </c>
       <c r="E198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F198" t="n">
-        <v>2</v>
+        <v>872</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5985,17 +5985,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>7.34</v>
+        <v>3.39</v>
       </c>
       <c r="E199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>872</v>
+        <v>679</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6013,23 +6013,23 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3.39</v>
+        <v>73.62</v>
       </c>
       <c r="E200" t="n">
+        <v>27</v>
+      </c>
+      <c r="F200" t="n">
+        <v>4414</v>
+      </c>
+      <c r="G200" t="n">
+        <v>3558.47</v>
+      </c>
+      <c r="H200" t="n">
         <v>1</v>
-      </c>
-      <c r="F200" t="n">
-        <v>679</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-      <c r="H200" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -6041,23 +6041,23 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>73.62</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>4414</v>
+        <v>8</v>
       </c>
       <c r="G201" t="n">
-        <v>3558.47</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -6069,17 +6069,17 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>7.97</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F202" t="n">
-        <v>8</v>
+        <v>4742</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -6097,17 +6097,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>7.97</v>
+        <v>22.3</v>
       </c>
       <c r="E203" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F203" t="n">
-        <v>4742</v>
+        <v>177</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6125,17 +6125,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>22.3</v>
+        <v>14.24</v>
       </c>
       <c r="E204" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>14.24</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>140</v>
+        <v>1117</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6181,17 +6181,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F206" t="n">
-        <v>1117</v>
+        <v>503</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6209,23 +6209,23 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>8.390000000000001</v>
+        <v>3.64</v>
       </c>
       <c r="E207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>571.1799999999999</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -6237,23 +6237,23 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>570</v>
+        <v>321</v>
       </c>
       <c r="G208" t="n">
-        <v>571.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -6265,17 +6265,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F209" t="n">
-        <v>321</v>
+        <v>126</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6293,17 +6293,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>14.25</v>
+        <v>6.35</v>
       </c>
       <c r="E210" t="n">
         <v>4</v>
       </c>
       <c r="F210" t="n">
-        <v>126</v>
+        <v>696</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6321,17 +6321,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>6.35</v>
+        <v>16.8</v>
       </c>
       <c r="E211" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F211" t="n">
-        <v>696</v>
+        <v>151</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>16.8</v>
+        <v>12.34</v>
       </c>
       <c r="E212" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F212" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6377,17 +6377,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>12.34</v>
+        <v>41.57</v>
       </c>
       <c r="E213" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F213" t="n">
-        <v>152</v>
+        <v>3260</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>41.57</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="E214" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F214" t="n">
-        <v>3260</v>
+        <v>1551</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6433,17 +6433,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>6.390000000000001</v>
+        <v>5.84</v>
       </c>
       <c r="E215" t="n">
         <v>2</v>
       </c>
       <c r="F215" t="n">
-        <v>1551</v>
+        <v>864</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6461,17 +6461,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>5.84</v>
+        <v>22.74</v>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F216" t="n">
-        <v>864</v>
+        <v>2730</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6489,17 +6489,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>22.74</v>
+        <v>7.12</v>
       </c>
       <c r="E217" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F217" t="n">
-        <v>2730</v>
+        <v>957</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6517,17 +6517,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>7.12</v>
+        <v>3.67</v>
       </c>
       <c r="E218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>957</v>
+        <v>700</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6545,17 +6545,17 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>3.67</v>
+        <v>13.74</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F219" t="n">
-        <v>700</v>
+        <v>1060</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6573,17 +6573,17 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>13.74</v>
+        <v>100.79</v>
       </c>
       <c r="E220" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="F220" t="n">
-        <v>1060</v>
+        <v>2349</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6596,22 +6596,22 @@
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>100.79</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>2349</v>
+        <v>2</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F224" t="n">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -6947,7 +6947,7 @@
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7077,17 +7077,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F238" t="n">
-        <v>185</v>
+        <v>258</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7105,17 +7105,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>258</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7133,17 +7133,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7161,17 +7161,17 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -7507,7 +7507,7 @@
         <v>0</v>
       </c>
       <c r="F253" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G253" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -7591,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D257" t="n">
@@ -7619,7 +7619,7 @@
         <v>0</v>
       </c>
       <c r="F257" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D258" t="n">
@@ -7647,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="F258" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
@@ -7665,7 +7665,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -7675,7 +7675,7 @@
         <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -7703,7 +7703,7 @@
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D261" t="n">
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G261" t="n">
         <v>0</v>
@@ -7749,17 +7749,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7772,78 +7772,78 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>4.8</v>
+        <v>6737.34</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>356</v>
       </c>
       <c r="F263" t="n">
-        <v>17</v>
+        <v>51246</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>12708.47</v>
       </c>
       <c r="H263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>6737.34</v>
+        <v>4.48</v>
       </c>
       <c r="E264" t="n">
-        <v>356</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>51247</v>
+        <v>141</v>
       </c>
       <c r="G264" t="n">
-        <v>12708.47</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>4.48</v>
+        <v>129.39</v>
       </c>
       <c r="E265" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F265" t="n">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7861,58 +7861,58 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>129.39</v>
+        <v>63.93</v>
       </c>
       <c r="E266" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F266" t="n">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>63.93</v>
+        <v>1283.67</v>
       </c>
       <c r="E267" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="F267" t="n">
-        <v>326</v>
+        <v>3608</v>
       </c>
       <c r="G267" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -7921,13 +7921,13 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1283.67</v>
+        <v>21.43</v>
       </c>
       <c r="E268" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="F268" t="n">
-        <v>3608</v>
+        <v>128</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -7940,22 +7940,22 @@
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>21.43</v>
+        <v>256.25</v>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F269" t="n">
-        <v>128</v>
+        <v>4228</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -7977,13 +7977,13 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>256.25</v>
+        <v>70.36</v>
       </c>
       <c r="E270" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F270" t="n">
-        <v>4228</v>
+        <v>2361</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -7996,22 +7996,22 @@
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>70.36</v>
+        <v>154.17</v>
       </c>
       <c r="E271" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F271" t="n">
-        <v>2361</v>
+        <v>1366</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
@@ -8024,22 +8024,22 @@
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>154.17</v>
+        <v>2093.83</v>
       </c>
       <c r="E272" t="n">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="F272" t="n">
-        <v>1366</v>
+        <v>31827</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -8052,35 +8052,35 @@
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>2093.83</v>
+        <v>814.17</v>
       </c>
       <c r="E273" t="n">
-        <v>203</v>
+        <v>146</v>
       </c>
       <c r="F273" t="n">
-        <v>31827</v>
+        <v>24891</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>5336.45</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -8089,26 +8089,26 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>814.17</v>
+        <v>2034.65</v>
       </c>
       <c r="E274" t="n">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="F274" t="n">
-        <v>24891</v>
+        <v>16894</v>
       </c>
       <c r="G274" t="n">
-        <v>5336.45</v>
+        <v>1778.82</v>
       </c>
       <c r="H274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -8117,26 +8117,26 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>2034.65</v>
+        <v>2351.04</v>
       </c>
       <c r="E275" t="n">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="F275" t="n">
-        <v>16894</v>
+        <v>9216</v>
       </c>
       <c r="G275" t="n">
-        <v>1778.82</v>
+        <v>7115.25</v>
       </c>
       <c r="H275" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -8145,26 +8145,26 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>2351.04</v>
+        <v>2145.98</v>
       </c>
       <c r="E276" t="n">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="F276" t="n">
-        <v>9216</v>
+        <v>16034</v>
       </c>
       <c r="G276" t="n">
-        <v>7115.25</v>
+        <v>10420.33</v>
       </c>
       <c r="H276" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -8173,54 +8173,54 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>2145.98</v>
+        <v>804.47</v>
       </c>
       <c r="E277" t="n">
-        <v>182</v>
+        <v>69</v>
       </c>
       <c r="F277" t="n">
-        <v>16034</v>
+        <v>39154</v>
       </c>
       <c r="G277" t="n">
-        <v>10420.33</v>
+        <v>1778.82</v>
       </c>
       <c r="H277" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>804.47</v>
+        <v>163.47</v>
       </c>
       <c r="E278" t="n">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="F278" t="n">
-        <v>39156</v>
+        <v>769</v>
       </c>
       <c r="G278" t="n">
-        <v>1778.82</v>
+        <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-Phrase-SP</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -8229,13 +8229,13 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>163.47</v>
+        <v>0</v>
       </c>
       <c r="E279" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>769</v>
+        <v>70</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
@@ -8248,22 +8248,22 @@
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-Phrase-SP</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>0</v>
+        <v>22.77</v>
       </c>
       <c r="E280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F280" t="n">
-        <v>70</v>
+        <v>439</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
@@ -8276,53 +8276,53 @@
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>22.77</v>
+        <v>3531.68</v>
       </c>
       <c r="E281" t="n">
-        <v>2</v>
+        <v>382</v>
       </c>
       <c r="F281" t="n">
-        <v>439</v>
+        <v>106429</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>5082.2</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>3531.68</v>
+        <v>2335.83</v>
       </c>
       <c r="E282" t="n">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="F282" t="n">
-        <v>106430</v>
+        <v>28794</v>
       </c>
       <c r="G282" t="n">
-        <v>5082.2</v>
+        <v>3388.14</v>
       </c>
       <c r="H282" t="n">
         <v>3</v>
@@ -8332,7 +8332,7 @@
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -8341,54 +8341,54 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2335.83</v>
+        <v>951.48</v>
       </c>
       <c r="E283" t="n">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="F283" t="n">
-        <v>28794</v>
+        <v>20747</v>
       </c>
       <c r="G283" t="n">
-        <v>3388.14</v>
+        <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>951.48</v>
+        <v>1175.23</v>
       </c>
       <c r="E284" t="n">
-        <v>54</v>
+        <v>376</v>
       </c>
       <c r="F284" t="n">
-        <v>20747</v>
+        <v>44074</v>
       </c>
       <c r="G284" t="n">
-        <v>0</v>
+        <v>14995.76</v>
       </c>
       <c r="H284" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -8397,54 +8397,54 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1175.23</v>
+        <v>21.5</v>
       </c>
       <c r="E285" t="n">
-        <v>376</v>
+        <v>5</v>
       </c>
       <c r="F285" t="n">
-        <v>44075</v>
+        <v>409</v>
       </c>
       <c r="G285" t="n">
-        <v>14995.76</v>
+        <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>21.5</v>
+        <v>969.78</v>
       </c>
       <c r="E286" t="n">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="F286" t="n">
-        <v>409</v>
+        <v>19148</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>2033.05</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8453,13 +8453,13 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>969.78</v>
+        <v>1411.55</v>
       </c>
       <c r="E287" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F287" t="n">
-        <v>19148</v>
+        <v>18841</v>
       </c>
       <c r="G287" t="n">
         <v>2033.05</v>
@@ -8472,7 +8472,7 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -8481,47 +8481,47 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1411.55</v>
+        <v>2688.64</v>
       </c>
       <c r="E288" t="n">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="F288" t="n">
-        <v>18841</v>
+        <v>46605</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>14211.03</v>
       </c>
       <c r="H288" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B08L46ZKKZ</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2688.64</v>
+        <v>2893.24</v>
       </c>
       <c r="E289" t="n">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="F289" t="n">
-        <v>46605</v>
+        <v>10576</v>
       </c>
       <c r="G289" t="n">
-        <v>14211.03</v>
+        <v>23950.45</v>
       </c>
       <c r="H289" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="290">
@@ -8533,86 +8533,86 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0FNQS4RRD</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2893.24</v>
+        <v>221.03</v>
       </c>
       <c r="E290" t="n">
-        <v>223</v>
+        <v>16</v>
       </c>
       <c r="F290" t="n">
-        <v>10576</v>
+        <v>5597</v>
       </c>
       <c r="G290" t="n">
-        <v>23950.45</v>
+        <v>5083.9</v>
       </c>
       <c r="H290" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>221.03</v>
+        <v>10.4</v>
       </c>
       <c r="E291" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F291" t="n">
-        <v>5597</v>
+        <v>47</v>
       </c>
       <c r="G291" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>10.4</v>
+        <v>478.88</v>
       </c>
       <c r="E292" t="n">
+        <v>37</v>
+      </c>
+      <c r="F292" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G292" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H292" t="n">
         <v>1</v>
-      </c>
-      <c r="F292" t="n">
-        <v>47</v>
-      </c>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8621,41 +8621,41 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>478.88</v>
+        <v>14.93</v>
       </c>
       <c r="E293" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F293" t="n">
-        <v>6300</v>
+        <v>457</v>
       </c>
       <c r="G293" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>14.93</v>
+        <v>612.2</v>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="F294" t="n">
-        <v>457</v>
+        <v>8614</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -8668,7 +8668,7 @@
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8677,26 +8677,26 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>612.2</v>
+        <v>3115.27</v>
       </c>
       <c r="E295" t="n">
-        <v>42</v>
+        <v>207</v>
       </c>
       <c r="F295" t="n">
-        <v>8614</v>
+        <v>11836</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>10928.8</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8705,26 +8705,26 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>3115.27</v>
+        <v>0</v>
       </c>
       <c r="E296" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>11836</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
-        <v>10928.8</v>
+        <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -8733,26 +8733,26 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>0</v>
+        <v>824.41</v>
       </c>
       <c r="E297" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F297" t="n">
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="G297" t="n">
-        <v>0</v>
+        <v>8005.92</v>
       </c>
       <c r="H297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -8761,41 +8761,41 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>824.41</v>
+        <v>0</v>
       </c>
       <c r="E298" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F298" t="n">
-        <v>2232</v>
+        <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>8005.92</v>
+        <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>0</v>
+        <v>1292.43</v>
       </c>
       <c r="E299" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>13336</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8817,26 +8817,26 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1292.43</v>
+        <v>575.8200000000001</v>
       </c>
       <c r="E300" t="n">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="F300" t="n">
-        <v>13336</v>
+        <v>2695</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8845,13 +8845,13 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>575.8200000000001</v>
+        <v>2091.94</v>
       </c>
       <c r="E301" t="n">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="F301" t="n">
-        <v>2695</v>
+        <v>16656</v>
       </c>
       <c r="G301" t="n">
         <v>5083.9</v>
@@ -8864,50 +8864,50 @@
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2091.94</v>
+        <v>102.12</v>
       </c>
       <c r="E302" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="F302" t="n">
-        <v>16656</v>
+        <v>175</v>
       </c>
       <c r="G302" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>102.12</v>
+        <v>1912.87</v>
       </c>
       <c r="E303" t="n">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="F303" t="n">
-        <v>175</v>
+        <v>34234</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -8920,7 +8920,7 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8929,19 +8929,19 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1912.87</v>
+        <v>2353.31</v>
       </c>
       <c r="E304" t="n">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="F304" t="n">
-        <v>34235</v>
+        <v>68973</v>
       </c>
       <c r="G304" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -9013,13 +9013,13 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>318.45</v>
+        <v>305.37</v>
       </c>
       <c r="E307" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F307" t="n">
-        <v>5527</v>
+        <v>5526</v>
       </c>
       <c r="G307" t="n">
         <v>5422.030000000001</v>
@@ -10691,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10754,19 +10754,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7595</v>
+        <v>11454</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>1618.996385151619</v>
+        <v>2543.753333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>3812.71</v>
+        <v>7568.639999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -10787,19 +10787,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10127</v>
+        <v>11454</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>2158.78357453683</v>
+        <v>2543.753333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>5083.9</v>
+        <v>7568.639999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -10820,19 +10820,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16642</v>
+        <v>11454</v>
       </c>
       <c r="E4" t="n">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>3853.480040311551</v>
+        <v>2543.753333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>10844.06</v>
+        <v>7568.639999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -10853,19 +10853,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10200</v>
+        <v>7163</v>
       </c>
       <c r="E5" t="n">
-        <v>388</v>
+        <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>3331.981226601305</v>
+        <v>2339.92</v>
       </c>
       <c r="G5" t="n">
-        <v>35485.28251748457</v>
+        <v>24919.925</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10886,19 +10886,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4126</v>
+        <v>7163</v>
       </c>
       <c r="E6" t="n">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="F6" t="n">
-        <v>1347.858773398696</v>
+        <v>2339.92</v>
       </c>
       <c r="G6" t="n">
-        <v>14354.56748251542</v>
+        <v>24919.925</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10919,19 +10919,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27143</v>
+        <v>9048</v>
       </c>
       <c r="E7" t="n">
-        <v>175</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>2220.08</v>
+        <v>740.0266666666666</v>
       </c>
       <c r="G7" t="n">
-        <v>5712.38</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -10943,28 +10943,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34215</v>
+        <v>9048</v>
       </c>
       <c r="E8" t="n">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="F8" t="n">
-        <v>3384.11</v>
+        <v>740.0266666666666</v>
       </c>
       <c r="G8" t="n">
-        <v>3140</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -10976,28 +10976,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1098</v>
+        <v>9048</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>719.965</v>
+        <v>740.0266666666666</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1904.126666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -11009,28 +11009,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1098</v>
+        <v>11405</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>719.965</v>
+        <v>1128.036666666667</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1046.666666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -11042,28 +11042,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4731</v>
+        <v>11405</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F11" t="n">
-        <v>161.1566666666667</v>
+        <v>1128.036666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1046.666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11075,28 +11075,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4731</v>
+        <v>11405</v>
       </c>
       <c r="E12" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>161.1566666666667</v>
+        <v>1128.036666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1046.666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -11108,22 +11108,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4731</v>
+        <v>1098</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>161.1566666666667</v>
+        <v>719.965</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11141,28 +11141,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24635</v>
+        <v>1098</v>
       </c>
       <c r="E14" t="n">
-        <v>249</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
-        <v>5252.228581436912</v>
+        <v>719.965</v>
       </c>
       <c r="G14" t="n">
-        <v>10760.16</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -11174,28 +11174,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13267</v>
+        <v>4731</v>
       </c>
       <c r="E15" t="n">
-        <v>248</v>
+        <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>2308.731418563088</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>15799.99</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -11207,22 +11207,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>645</v>
+        <v>4731</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>119.7</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -11240,22 +11240,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>645</v>
+        <v>4731</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>119.7</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -11273,28 +11273,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>645</v>
+        <v>37902</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>497</v>
       </c>
       <c r="F18" t="n">
-        <v>119.7</v>
+        <v>7560.96</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>23849.13</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11315,19 +11315,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2272</v>
+        <v>645</v>
       </c>
       <c r="E19" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>602.71</v>
+        <v>119.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2541.52</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -11339,28 +11339,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>378.5</v>
+        <v>119.7</v>
       </c>
       <c r="G20" t="n">
-        <v>2380</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11372,28 +11372,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11965</v>
+        <v>645</v>
       </c>
       <c r="E21" t="n">
-        <v>414</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>6128.317655086619</v>
+        <v>119.7</v>
       </c>
       <c r="G21" t="n">
-        <v>29271.07713991251</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11405,28 +11405,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3828</v>
+        <v>2272</v>
       </c>
       <c r="E22" t="n">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>1960.772344913381</v>
+        <v>602.71</v>
       </c>
       <c r="G22" t="n">
-        <v>9365.362860087493</v>
+        <v>2541.52</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11438,25 +11438,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>66.19</v>
+        <v>189.25</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -11471,25 +11471,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="E24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>66.19</v>
+        <v>189.25</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1190</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -11504,28 +11504,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>354</v>
+        <v>15793</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>546</v>
       </c>
       <c r="F25" t="n">
-        <v>66.19</v>
+        <v>8089.09</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>41516.11</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11537,28 +11537,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13043</v>
+        <v>354</v>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>643.292985708973</v>
+        <v>66.19</v>
       </c>
       <c r="G26" t="n">
-        <v>3023.883416210665</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11570,25 +11570,25 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2299</v>
+        <v>354</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3670142910269</v>
+        <v>66.19</v>
       </c>
       <c r="G27" t="n">
-        <v>532.8965837893358</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -11603,28 +11603,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5221</v>
+        <v>354</v>
       </c>
       <c r="E28" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>691.435990895176</v>
+        <v>66.19</v>
       </c>
       <c r="G28" t="n">
-        <v>7918.965081720772</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11636,28 +11636,28 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4561</v>
+        <v>5114</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>603.9923698418058</v>
+        <v>252.22</v>
       </c>
       <c r="G29" t="n">
-        <v>6917.479780320195</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11669,28 +11669,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10802</v>
+        <v>5114</v>
       </c>
       <c r="E30" t="n">
-        <v>118</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>1430.64746700817</v>
+        <v>252.22</v>
       </c>
       <c r="G30" t="n">
-        <v>16385.09924949441</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11711,19 +11711,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5850</v>
+        <v>5114</v>
       </c>
       <c r="E31" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>774.8245302200332</v>
+        <v>252.22</v>
       </c>
       <c r="G31" t="n">
-        <v>8874.0078330741</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11740,23 +11740,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1020</v>
+        <v>9151</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="F32" t="n">
-        <v>135.0596420348141</v>
+        <v>1211.986666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>1546.828055390516</v>
+        <v>15575.42666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11768,28 +11768,28 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12198</v>
+        <v>9151</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="F33" t="n">
-        <v>471.15</v>
+        <v>1211.986666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>15575.42666666667</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11801,28 +11801,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12198</v>
+        <v>9151</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>471.15</v>
+        <v>1211.986666666667</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>15575.42666666667</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11834,28 +11834,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1104</v>
+        <v>12198</v>
       </c>
       <c r="E35" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F35" t="n">
-        <v>934.7929997709824</v>
+        <v>471.15</v>
       </c>
       <c r="G35" t="n">
-        <v>7625.420000000001</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11867,28 +11867,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>736</v>
+        <v>12198</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F36" t="n">
-        <v>623.2304753752182</v>
+        <v>471.15</v>
       </c>
       <c r="G36" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11905,23 +11905,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1655</v>
+        <v>1165</v>
       </c>
       <c r="E37" t="n">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>1402.0865248538</v>
+        <v>986.7033333333334</v>
       </c>
       <c r="G37" t="n">
-        <v>11437.29</v>
+        <v>8048.87</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -11933,28 +11933,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>1165</v>
       </c>
       <c r="E38" t="n">
+        <v>55</v>
+      </c>
+      <c r="F38" t="n">
+        <v>986.7033333333334</v>
+      </c>
+      <c r="G38" t="n">
+        <v>8048.87</v>
+      </c>
+      <c r="H38" t="n">
         <v>2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11966,28 +11966,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>1165</v>
       </c>
       <c r="E39" t="n">
+        <v>55</v>
+      </c>
+      <c r="F39" t="n">
+        <v>986.7033333333334</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8048.87</v>
+      </c>
+      <c r="H39" t="n">
         <v>2</v>
-      </c>
-      <c r="F39" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12032,22 +12032,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1315</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>53.05666666666666</v>
+        <v>31.9</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -12065,22 +12065,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1315</v>
+        <v>27</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>53.05666666666666</v>
+        <v>31.9</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12122,6 +12122,72 @@
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>53.05666666666666</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E45" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" t="n">
+        <v>53.05666666666666</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H310"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,22 +576,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_MR-01_B0CYSLCRQS_Brand_HV_MV_LV_Phrase &amp; Exact</t>
+          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>330.73</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1192</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -604,22 +604,22 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_SC-04_B0DNJS23HS_HV_Exact</t>
+          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_Gen_HV_Exact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>330.73</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1192</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -632,12 +632,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_ST-03_B0GN8WW6BC_Gen_HV_Exact</t>
+          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -660,12 +660,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nex_HnK_SP_KT_VC-01_B0DCGHVN81_HV_Phrase &amp; Exact</t>
+          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -688,12 +688,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-02_B0GN94YDY2</t>
+          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -716,50 +716,50 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nex_Hnk_SP_PT_ST-03_B0GN8WW6BC</t>
+          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3995.06</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>79954</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2795.76</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev -  B0D2LKB4BJ - Hair Styling Straightener - Auto</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>886.8200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3536</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -772,7 +772,7 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Exact/BM</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -781,26 +781,26 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5511.35</v>
+        <v>1345.68</v>
       </c>
       <c r="E13" t="n">
-        <v>356</v>
+        <v>103</v>
       </c>
       <c r="F13" t="n">
-        <v>91388</v>
+        <v>4435</v>
       </c>
       <c r="G13" t="n">
-        <v>5464.4</v>
+        <v>3812.71</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - CT</t>
+          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -809,306 +809,306 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1435.47</v>
+        <v>3724.74</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>215</v>
       </c>
       <c r="F14" t="n">
-        <v>4946</v>
+        <v>18541</v>
       </c>
       <c r="G14" t="n">
-        <v>5083.9</v>
+        <v>4235.59</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2620.63</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7286</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3812.71</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev - B0CDPP45BM - Steam Cleaner - PT 2</t>
+          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4190.45</v>
+        <v>792.71</v>
       </c>
       <c r="E16" t="n">
-        <v>242</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>19523</v>
+        <v>6641</v>
       </c>
       <c r="G16" t="n">
-        <v>4235.59</v>
+        <v>1694.07</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - Auto</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>179.1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4927</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>846.61</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev - B0D383WQPB - Garment Steamer - PT</t>
+          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>792.71</v>
+        <v>207.88</v>
       </c>
       <c r="E18" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>6875</v>
+        <v>3671</v>
       </c>
       <c r="G18" t="n">
-        <v>1694.07</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - BM 2</t>
+          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>223.97</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5448</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>846.61</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev - B0D81DLSFT - Blow Dryer - PT</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>427.55</v>
+        <v>35.59</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>7241</v>
+        <v>1951</v>
       </c>
       <c r="G20" t="n">
-        <v>846.61</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev - B0D9KCNVNM - Oscillating Tooth Brush - Broad</t>
+          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1305.06</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>4959</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1694.06</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - AT</t>
+          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61.37</v>
+        <v>822.6</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>2988</v>
+        <v>16227</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1295.76</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCGHKRXX - Therapy Comb - SP - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1493.69</v>
+        <v>2433.08</v>
       </c>
       <c r="E23" t="n">
-        <v>38</v>
+        <v>202</v>
       </c>
       <c r="F23" t="n">
-        <v>5428</v>
+        <v>9504</v>
       </c>
       <c r="G23" t="n">
-        <v>1694.06</v>
+        <v>11522.04</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK4DR1B - Skin Lift Device - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1252.29</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>31833</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2989.83</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Broad1</t>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner- KT - Com - Exact</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1117,26 +1117,26 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2810.94</v>
+        <v>247.53</v>
       </c>
       <c r="E25" t="n">
-        <v>237</v>
+        <v>13</v>
       </c>
       <c r="F25" t="n">
-        <v>10674</v>
+        <v>4504</v>
       </c>
       <c r="G25" t="n">
-        <v>11522.04</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - KT - Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2015.67</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>25584</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner- KT - Com - Exact</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>247.53</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4504</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1201,26 +1201,26 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2015.67</v>
+        <v>1372.76</v>
       </c>
       <c r="E28" t="n">
-        <v>230</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>25586</v>
+        <v>5098</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1248,7 +1248,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine - PT 2</t>
+          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1257,26 +1257,26 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1612.91</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>5718</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- Exact</t>
+          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1285,31 +1285,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>162.75</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4934</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>5761.02</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P - Sofa Cleaning Machine- PT/CT</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1332,78 +1332,78 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev - B0DCK7ZH5P- Sofa Cleaning Machine - Auto</t>
+          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>162.75</v>
+        <v>294.02</v>
       </c>
       <c r="E33" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F33" t="n">
-        <v>4936</v>
+        <v>8768</v>
       </c>
       <c r="G33" t="n">
-        <v>5761.02</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Auto</t>
+          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3906.26</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>20032</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>11900</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev - B0DDC3GVZW - Cordless Vacuum Cleaner - Phrase</t>
+          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>317.29</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>10443</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1416,78 +1416,78 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev - B0DKK15YNJ - Oil Applicator Comb - SP - AT</t>
+          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DMT19RWC</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4226.45</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>21140</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>14280</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nexlev - B0DM6BB3VT - Calf Massager - SP - KT - Exact</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1809.59</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>31145</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>10371.18</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev - B0DMT19RWC - Massage Gun - Auto</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DMT19RWC</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>883.5400000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3357</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - BM</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1509,26 +1509,26 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2390.65</v>
+        <v>1053.12</v>
       </c>
       <c r="E39" t="n">
-        <v>154</v>
+        <v>64</v>
       </c>
       <c r="F39" t="n">
-        <v>34488</v>
+        <v>8307</v>
       </c>
       <c r="G39" t="n">
-        <v>10371.18</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1537,13 +1537,13 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1204.67</v>
+        <v>2110.36</v>
       </c>
       <c r="E40" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F40" t="n">
-        <v>4261</v>
+        <v>1201</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1556,7 +1556,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - CT - On Other</t>
+          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1433.95</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>10185</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1584,22 +1584,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - PT</t>
+          <t>Nexlev - B0DQCWRG3H -  Ionic 3 in 1 Hot Air Brush - SP - AT - 00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2440.26</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1543</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1612,12 +1612,12 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nexlev - B0DNJS23HS - Steam Cleaner - Phrase/BM</t>
+          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1640,40 +1640,40 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nexlev - B0DQCWRG3H -  Ionic 3 in 1 Hot Air Brush - SP - AT - 00</t>
+          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>3218.67</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>53041</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>15251.7</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nexlev - B0DV94R4QD - Massager Gun - Auto</t>
+          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1696,35 +1696,35 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nexlev - B0DVC7VJP1 - Stand Mixer - Broad</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3636.03</v>
+        <v>784</v>
       </c>
       <c r="E46" t="n">
-        <v>276</v>
+        <v>48</v>
       </c>
       <c r="F46" t="n">
-        <v>59260</v>
+        <v>20997</v>
       </c>
       <c r="G46" t="n">
-        <v>15251.7</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 -  Steam Cleaner 00 - KT - Exact</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1733,26 +1733,26 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>882.46</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2203</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - BM</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1056.81</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>25331</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - CT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1789,26 +1789,26 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1380.68</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3433</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>7752.539999999999</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - PT</t>
+          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1817,82 +1817,82 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>14235.42</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>766</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>106019</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>42105.92</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - Phrase</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>2336.94</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>84290</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>24396.6</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nexlev - B0F43P6D23 - Steam Cleaner - SP - KT - Exact</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>15787.19</v>
+        <v>2584.8</v>
       </c>
       <c r="E52" t="n">
-        <v>839</v>
+        <v>169</v>
       </c>
       <c r="F52" t="n">
-        <v>111940</v>
+        <v>26399</v>
       </c>
       <c r="G52" t="n">
-        <v>42105.92</v>
+        <v>2033.05</v>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - BM</t>
+          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1901,44 +1901,44 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3093.65</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>105888</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>24396.6</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - PT</t>
+          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3004.94</v>
+        <v>54.73999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>197</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>31068</v>
+        <v>675</v>
       </c>
       <c r="G54" t="n">
-        <v>2033.05</v>
+        <v>1948.31</v>
       </c>
       <c r="H54" t="n">
         <v>1</v>
@@ -1948,22 +1948,22 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nexlev - B0FS6TB7CP - Portable Blender - Phrase</t>
+          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1976,91 +1976,91 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nexlev - SP- B0GN86G345 -  Car Air Purifier - BM</t>
+          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>63.48</v>
+        <v>16173.27</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>647</v>
       </c>
       <c r="F56" t="n">
-        <v>745</v>
+        <v>89695</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>53120.33</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nexlev - SP-B0GN94YDY2 - Stand Mixer with Digital Timer - BM</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.87</v>
+        <v>2564.04</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="F57" t="n">
-        <v>103</v>
+        <v>9787</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>7878.8</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nexlev -B0CDPP45BM-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>17474.69</v>
+        <v>803.15</v>
       </c>
       <c r="E58" t="n">
-        <v>701</v>
+        <v>41</v>
       </c>
       <c r="F58" t="n">
-        <v>94195</v>
+        <v>2410</v>
       </c>
       <c r="G58" t="n">
-        <v>53120.33</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner -SP-PT</t>
+          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2069,16 +2069,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2882.58</v>
+        <v>1175.62</v>
       </c>
       <c r="E59" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="F59" t="n">
-        <v>10312</v>
+        <v>2765</v>
       </c>
       <c r="G59" t="n">
-        <v>7878.8</v>
+        <v>5083.05</v>
       </c>
       <c r="H59" t="n">
         <v>2</v>
@@ -2088,68 +2088,68 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS- Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1029.15</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>3361</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2541.53</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nexlev -B0CYSLCRQS-Vacuum Cleaner-SP-KT-Broad</t>
+          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1476.6</v>
+        <v>515.51</v>
       </c>
       <c r="E61" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="F61" t="n">
-        <v>3383</v>
+        <v>1696</v>
       </c>
       <c r="G61" t="n">
-        <v>5083.05</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nexlev -B0D2LHNS9B- Callus Remover-SP-PT</t>
+          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2172,152 +2172,152 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nexlev -B0D9KFZYG8-Face Steam-SP-CT</t>
+          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>667.92</v>
+        <v>1534.17</v>
       </c>
       <c r="E63" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="F63" t="n">
-        <v>1945</v>
+        <v>3139</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nexlev -B0DKJXRXKM- Remover Tool -SP-CT</t>
+          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>3328.84</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>29932</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>6015.26</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nexlev -B0DNJS23HS-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1883.16</v>
+        <v>2406.86</v>
       </c>
       <c r="E65" t="n">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="F65" t="n">
-        <v>3324</v>
+        <v>4868</v>
       </c>
       <c r="G65" t="n">
-        <v>5083.9</v>
+        <v>20503.39</v>
       </c>
       <c r="H65" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23 - Steam Cleaner-SP-KT -Broad</t>
+          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FPGDVVCX</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4829.18</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>38085</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>14105.93</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nexlev -B0F43P6D23-Steam Cleaner-SP-PT</t>
+          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3041.94</v>
+        <v>518.04</v>
       </c>
       <c r="E67" t="n">
-        <v>224</v>
+        <v>76</v>
       </c>
       <c r="F67" t="n">
-        <v>5203</v>
+        <v>8279</v>
       </c>
       <c r="G67" t="n">
-        <v>14233.05</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nexlev -B0FPGDVVCX- Calf Massager-SP-Auto</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2340,22 +2340,22 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nexlev -B0GKNGWLJ2- Cordless Spin -SP-KT-Exact</t>
+          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>542.5599999999999</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>8832</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2368,12 +2368,12 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2396,12 +2396,12 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-Tyre Inflator-SP-CT</t>
+          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2424,22 +2424,22 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0GN8N96R5</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>15.72</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2452,119 +2452,119 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nexlev -Multi Ad Group-Lint Remover-SP-PT</t>
+          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1303.17</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>6130</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>14996.61</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nexlev -SP- B0GN8N96R5 - Smart Air Purifier - BM</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>B0GN8N96R5</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.72</v>
+        <v>4287.27</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>170</v>
       </c>
       <c r="F74" t="n">
-        <v>937</v>
+        <v>22736</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3812.71</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM- Steam Cleaner-SP-KT-Exact-Branded</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1526.85</v>
+        <v>1077.15</v>
       </c>
       <c r="E75" t="n">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="F75" t="n">
-        <v>6530</v>
+        <v>8672</v>
       </c>
       <c r="G75" t="n">
-        <v>14996.61</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4739.67</v>
+        <v>1069.46</v>
       </c>
       <c r="E76" t="n">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="F76" t="n">
-        <v>24739</v>
+        <v>2891</v>
       </c>
       <c r="G76" t="n">
-        <v>3812.71</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner -SP -KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1077.15</v>
+        <v>1208.54</v>
       </c>
       <c r="E77" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F77" t="n">
-        <v>8672</v>
+        <v>10648</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-CT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1342.38</v>
+        <v>1686.03</v>
       </c>
       <c r="E78" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F78" t="n">
-        <v>3292</v>
+        <v>5499</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2620,22 +2620,22 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS- Vacuum Cleaner-SP-KT-Phrase/Broad</t>
+          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LHNS9B</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1443.32</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>12487</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2648,22 +2648,22 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SP-KT-Phrase</t>
+          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1961.47</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>8031</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2676,12 +2676,12 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B- Callus Remover -SP-CT</t>
+          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2704,12 +2704,12 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LHNS9B-Callus Remover-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2732,12 +2732,12 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nexlev-B0D2LJSQXZ- Steam Mop- SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -2760,50 +2760,50 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nexlev-B0D383WQPB-Garment Steamer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>681.78</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>8486</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1046.67</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>107.26</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2816,165 +2816,165 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nexlev-B0D672NXC8-Steam Cleaner-SP-PT</t>
+          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1757.06</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>39492</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2879.66</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-KT-Phrase</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>763.83</v>
+        <v>129.41</v>
       </c>
       <c r="E87" t="n">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="F87" t="n">
-        <v>9474</v>
+        <v>902</v>
       </c>
       <c r="G87" t="n">
-        <v>1046.67</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nexlev-B0D67727VG-Oil Applicator-SP-PT</t>
+          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>123.42</v>
+        <v>623.73</v>
       </c>
       <c r="E88" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
-        <v>248</v>
+        <v>13369</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>2856.19</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nexlev-B0D9KFZYG8- Face Steam-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1997.36</v>
+        <v>228.38</v>
       </c>
       <c r="E89" t="n">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="F89" t="n">
-        <v>44910</v>
+        <v>1818</v>
       </c>
       <c r="G89" t="n">
-        <v>2879.66</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -Exact</t>
+          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>129.41</v>
+        <v>328.93</v>
       </c>
       <c r="E90" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F90" t="n">
-        <v>902</v>
+        <v>2221</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>2287.29</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCGHVN81-Vacuum Cleaner -SP-Auto</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>623.73</v>
+        <v>2852.36</v>
       </c>
       <c r="E91" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="F91" t="n">
-        <v>13371</v>
+        <v>24104</v>
       </c>
       <c r="G91" t="n">
-        <v>2856.19</v>
+        <v>2880.5</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
@@ -2984,22 +2984,22 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener--SP-KT-Phrase</t>
+          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>246.15</v>
+        <v>616.8</v>
       </c>
       <c r="E92" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F92" t="n">
-        <v>2097</v>
+        <v>810</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -3012,147 +3012,147 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK3N2JJ-Hair Straightener-SP-PT</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>430.81</v>
+        <v>760.1</v>
       </c>
       <c r="E93" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F93" t="n">
-        <v>2380</v>
+        <v>1829</v>
       </c>
       <c r="G93" t="n">
-        <v>2287.29</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3251.47</v>
+        <v>632.42</v>
       </c>
       <c r="E94" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="F94" t="n">
-        <v>26510</v>
+        <v>11510</v>
       </c>
       <c r="G94" t="n">
-        <v>2880.5</v>
+        <v>9233.34</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nexlev-B0DCK7ZH5P-Vacuum Cleaner-SP-PT</t>
+          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>616.8</v>
+        <v>2996.33</v>
       </c>
       <c r="E95" t="n">
-        <v>27</v>
+        <v>175</v>
       </c>
       <c r="F95" t="n">
-        <v>810</v>
+        <v>31363</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>27011.86</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator--SP-KT-Phrase</t>
+          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>904.25</v>
+        <v>1833.79</v>
       </c>
       <c r="E96" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="F96" t="n">
-        <v>2207</v>
+        <v>3707</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ-Oil Applicator-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>705.3299999999999</v>
+        <v>408.64</v>
       </c>
       <c r="E97" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F97" t="n">
-        <v>12645</v>
+        <v>1844</v>
       </c>
       <c r="G97" t="n">
-        <v>11613.34</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS -Steam Cleaner-SP-KT-Branded</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3161,184 +3161,184 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3608.31</v>
+        <v>3294.22</v>
       </c>
       <c r="E98" t="n">
-        <v>204</v>
+        <v>113</v>
       </c>
       <c r="F98" t="n">
-        <v>34801</v>
+        <v>9504</v>
       </c>
       <c r="G98" t="n">
-        <v>27011.86</v>
+        <v>5083.9</v>
       </c>
       <c r="H98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS- Steam Cleaner-SP-KT-Broad</t>
+          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2158.58</v>
+        <v>1009.24</v>
       </c>
       <c r="E99" t="n">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F99" t="n">
-        <v>4285</v>
+        <v>16240</v>
       </c>
       <c r="G99" t="n">
-        <v>5083.9</v>
+        <v>3472.88</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-CT Refine</t>
+          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>539.4400000000001</v>
+        <v>1935.92</v>
       </c>
       <c r="E100" t="n">
-        <v>11</v>
+        <v>179</v>
       </c>
       <c r="F100" t="n">
-        <v>2391</v>
+        <v>31751</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1736.44</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SP-KT -Exact/Phrase</t>
+          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>3976.73</v>
+        <v>1571.18</v>
       </c>
       <c r="E101" t="n">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="F101" t="n">
-        <v>10083</v>
+        <v>83754</v>
       </c>
       <c r="G101" t="n">
-        <v>5083.9</v>
+        <v>20335.6</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H- Hot Air Brush-SP-KT-Exact</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1147.53</v>
+        <v>1578.64</v>
       </c>
       <c r="E102" t="n">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="F102" t="n">
-        <v>18221</v>
+        <v>19485</v>
       </c>
       <c r="G102" t="n">
-        <v>1736.44</v>
+        <v>20335.6</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexlev-B0DQCWRG3H-Hot Air Brush- SP-KT-Phrase</t>
+          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>2299.48</v>
+        <v>363.83</v>
       </c>
       <c r="E103" t="n">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="F103" t="n">
-        <v>39930</v>
+        <v>1393</v>
       </c>
       <c r="G103" t="n">
-        <v>1736.44</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1- Stand Mixer- SP-Auto</t>
+          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1685.3</v>
+        <v>3898.89</v>
       </c>
       <c r="E104" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="F104" t="n">
-        <v>87579</v>
+        <v>17114</v>
       </c>
       <c r="G104" t="n">
-        <v>20335.6</v>
+        <v>11225.42</v>
       </c>
       <c r="H104" t="n">
         <v>4</v>
@@ -3348,50 +3348,50 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1824.54</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>20484</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>20335.6</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nexlev-B0DVC7VJP1-Stand Mixer-SP-PT</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>484.76</v>
+        <v>84</v>
       </c>
       <c r="E106" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F106" t="n">
-        <v>2037</v>
+        <v>652</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3404,7 +3404,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23 -Steam Cleaner- SP-KT-Exact</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3413,156 +3413,156 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>4617.18</v>
+        <v>13856.71</v>
       </c>
       <c r="E107" t="n">
-        <v>189</v>
+        <v>805</v>
       </c>
       <c r="F107" t="n">
-        <v>18756</v>
+        <v>51814</v>
       </c>
       <c r="G107" t="n">
-        <v>13894.06</v>
+        <v>75020.3</v>
       </c>
       <c r="H107" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23- Steam Cleaner-SP-Auto</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>7885.32</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>325658</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>10165.26</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner -SP-CT</t>
+          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>84</v>
+        <v>945.5599999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="F109" t="n">
-        <v>956</v>
+        <v>34599</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>2033.05</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>14794.85</v>
+        <v>193.91</v>
       </c>
       <c r="E110" t="n">
-        <v>854</v>
+        <v>27</v>
       </c>
       <c r="F110" t="n">
-        <v>54869</v>
+        <v>2823</v>
       </c>
       <c r="G110" t="n">
-        <v>74723.69</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender -SP-KT-Exact/Phrase</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9195.870000000001</v>
+        <v>1155.72</v>
       </c>
       <c r="E111" t="n">
-        <v>710</v>
+        <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>370895</v>
+        <v>17050</v>
       </c>
       <c r="G111" t="n">
-        <v>14231.37</v>
+        <v>4320.34</v>
       </c>
       <c r="H111" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-Auto</t>
+          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1010.91</v>
+        <v>497.69</v>
       </c>
       <c r="E112" t="n">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="F112" t="n">
-        <v>38284</v>
+        <v>5412</v>
       </c>
       <c r="G112" t="n">
-        <v>2033.05</v>
+        <v>1439.84</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
@@ -3572,12 +3572,12 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nexlev-B0FS6TB7CP-Portable Blender-SP-CT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -3587,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>193.91</v>
+        <v>30.7</v>
       </c>
       <c r="E114" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F114" t="n">
-        <v>2823</v>
+        <v>4107</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3628,56 +3628,56 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-Exact/Phrase</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1468.22</v>
+        <v>21.3</v>
       </c>
       <c r="E115" t="n">
-        <v>123</v>
+        <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>23461</v>
+        <v>504</v>
       </c>
       <c r="G115" t="n">
-        <v>4320.34</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nexlev-B0GKNGWLJ2-Cordless Spin-SP-KT-PT</t>
+          <t>Nexlev-Branded-All Products</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>497.69</v>
+        <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>5413</v>
+        <v>126</v>
       </c>
       <c r="G116" t="n">
-        <v>1439.84</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3689,17 +3689,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>20.24</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3717,17 +3717,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>46.22</v>
+        <v>6.85</v>
       </c>
       <c r="E118" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>4857</v>
+        <v>251</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3745,17 +3745,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>27.64</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>1315</v>
+        <v>219</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3773,23 +3773,23 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>37.64</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F120" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>951.4299999999999</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -3801,17 +3801,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>31.07</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3829,17 +3829,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>6.85</v>
+        <v>29.8</v>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F122" t="n">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3857,23 +3857,23 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>67.74000000000001</v>
       </c>
       <c r="E123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F123" t="n">
-        <v>240</v>
+        <v>4091</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>761.86</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>48.64</v>
+        <v>4.65</v>
       </c>
       <c r="E124" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="G124" t="n">
-        <v>951.4299999999999</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3941,17 +3941,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>32.79</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>354</v>
+        <v>129</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3969,23 +3969,23 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>74.53999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="E127" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F127" t="n">
-        <v>4277</v>
+        <v>239</v>
       </c>
       <c r="G127" t="n">
-        <v>761.86</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -3997,17 +3997,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4.65</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>91</v>
+        <v>593</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -4025,17 +4025,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>6.77</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -4053,17 +4053,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>24.15</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F130" t="n">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -4081,17 +4081,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.2</v>
+        <v>27.24</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>273</v>
+        <v>72</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -4109,23 +4109,23 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>9.949999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="E132" t="n">
+        <v>10</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1478</v>
+      </c>
+      <c r="G132" t="n">
+        <v>3465.26</v>
+      </c>
+      <c r="H132" t="n">
         <v>2</v>
-      </c>
-      <c r="F132" t="n">
-        <v>699</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -4137,23 +4137,23 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6.77</v>
+        <v>137.79</v>
       </c>
       <c r="E133" t="n">
+        <v>21</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2125</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1771.19</v>
+      </c>
+      <c r="H133" t="n">
         <v>1</v>
-      </c>
-      <c r="F133" t="n">
-        <v>146</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -4165,17 +4165,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>30.34</v>
+        <v>6.71</v>
       </c>
       <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
         <v>6</v>
-      </c>
-      <c r="F134" t="n">
-        <v>375</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -4193,17 +4193,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>34.04</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -4221,23 +4221,23 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>58.04</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>1687</v>
+        <v>8</v>
       </c>
       <c r="G136" t="n">
-        <v>3465.26</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -4249,23 +4249,23 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>166.42</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>2358</v>
+        <v>24</v>
       </c>
       <c r="G137" t="n">
-        <v>1771.19</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -4277,23 +4277,23 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>6.71</v>
+        <v>292.44</v>
       </c>
       <c r="E138" t="n">
+        <v>44</v>
+      </c>
+      <c r="F138" t="n">
+        <v>5687</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1948.31</v>
+      </c>
+      <c r="H138" t="n">
         <v>1</v>
-      </c>
-      <c r="F138" t="n">
-        <v>6</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -4305,17 +4305,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>99.17</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F139" t="n">
-        <v>9</v>
+        <v>2582</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4361,17 +4361,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>338.82</v>
+        <v>13.56</v>
       </c>
       <c r="E142" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="F142" t="n">
-        <v>6041</v>
+        <v>79</v>
       </c>
       <c r="G142" t="n">
-        <v>1948.31</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -4417,17 +4417,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>112.75</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>2601</v>
+        <v>69</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4445,17 +4445,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>39.98</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F144" t="n">
-        <v>103</v>
+        <v>387</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4501,17 +4501,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>13.56</v>
+        <v>14.5</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
       </c>
       <c r="F146" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -4539,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4557,17 +4557,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>53.49</v>
+        <v>53.42</v>
       </c>
       <c r="E148" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F148" t="n">
-        <v>600</v>
+        <v>274</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4585,17 +4585,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>26.51</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F149" t="n">
-        <v>9</v>
+        <v>2122</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4613,17 +4613,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>14.5</v>
+        <v>37.52</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F150" t="n">
-        <v>39</v>
+        <v>2934</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4641,17 +4641,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>14.85</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F151" t="n">
-        <v>174</v>
+        <v>472</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4669,17 +4669,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>357</v>
+        <v>115</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>35.57</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>2887</v>
+        <v>418</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4725,17 +4725,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>37.52</v>
+        <v>1.3</v>
       </c>
       <c r="E154" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>3091</v>
+        <v>122</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4753,17 +4753,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>14.85</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>543</v>
+        <v>1826</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4781,23 +4781,23 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>44.66</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F156" t="n">
-        <v>134</v>
+        <v>7284</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>168.64</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -4809,17 +4809,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>2.33</v>
+        <v>6.119999999999999</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F157" t="n">
-        <v>447</v>
+        <v>121</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4837,17 +4837,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4865,17 +4865,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>66</v>
+        <v>321</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>1873</v>
+        <v>256</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4921,23 +4921,23 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>57.09999999999999</v>
+        <v>13.01</v>
       </c>
       <c r="E161" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F161" t="n">
-        <v>7882</v>
+        <v>82</v>
       </c>
       <c r="G161" t="n">
-        <v>168.64</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -4949,23 +4949,23 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>6.119999999999999</v>
+        <v>40.09</v>
       </c>
       <c r="E162" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F162" t="n">
-        <v>140</v>
+        <v>1770</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>338.14</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -4977,45 +4977,45 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>155.58</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F163" t="n">
-        <v>265</v>
+        <v>4581</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>8466.1</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0CDQ55W2M</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6.68</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -5028,22 +5028,22 @@
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>13.97</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F165" t="n">
-        <v>286</v>
+        <v>956</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -5056,22 +5056,22 @@
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>17.05</v>
+        <v>4.77</v>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>92</v>
+        <v>582</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -5084,56 +5084,56 @@
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>46.89</v>
+        <v>10.5</v>
       </c>
       <c r="E167" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F167" t="n">
-        <v>2321</v>
+        <v>602</v>
       </c>
       <c r="G167" t="n">
-        <v>672.89</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Nexlev-Branded-All Products</t>
+          <t>Nexlev-Catch All-AT</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>173.45</v>
+        <v>26.81</v>
       </c>
       <c r="E168" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F168" t="n">
-        <v>4765</v>
+        <v>7882</v>
       </c>
       <c r="G168" t="n">
-        <v>13550</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -5145,23 +5145,23 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>B0CDQ55W2M</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0</v>
+        <v>31.41</v>
       </c>
       <c r="E169" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F169" t="n">
-        <v>83</v>
+        <v>2212</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>677.12</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -5173,17 +5173,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>15.4</v>
+        <v>20.71</v>
       </c>
       <c r="E170" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F170" t="n">
-        <v>1099</v>
+        <v>1893</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -5201,17 +5201,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>7.77</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>829</v>
+        <v>658</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -5229,17 +5229,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.5</v>
+        <v>7.76</v>
       </c>
       <c r="E172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F172" t="n">
-        <v>603</v>
+        <v>2165</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -5257,17 +5257,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>35.81</v>
+        <v>3.65</v>
       </c>
       <c r="E173" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F173" t="n">
-        <v>8993</v>
+        <v>1236</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -5285,20 +5285,20 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>36.89</v>
+        <v>24.8</v>
       </c>
       <c r="E174" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F174" t="n">
-        <v>2445</v>
+        <v>1442</v>
       </c>
       <c r="G174" t="n">
-        <v>677.12</v>
+        <v>761.86</v>
       </c>
       <c r="H174" t="n">
         <v>1</v>
@@ -5313,17 +5313,17 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>26.59</v>
+        <v>1.75</v>
       </c>
       <c r="E175" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F175" t="n">
-        <v>2091</v>
+        <v>10311</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -5341,17 +5341,17 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>7.57</v>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F176" t="n">
-        <v>680</v>
+        <v>634</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7.76</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="E177" t="n">
         <v>4</v>
       </c>
       <c r="F177" t="n">
-        <v>2303</v>
+        <v>871</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5397,17 +5397,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>3.65</v>
+        <v>54.86</v>
       </c>
       <c r="E178" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F178" t="n">
-        <v>1347</v>
+        <v>4412</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5425,23 +5425,23 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>27.8</v>
+        <v>10.33</v>
       </c>
       <c r="E179" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F179" t="n">
-        <v>1568</v>
+        <v>466</v>
       </c>
       <c r="G179" t="n">
-        <v>761.86</v>
+        <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -5453,17 +5453,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>2.75</v>
+        <v>3.67</v>
       </c>
       <c r="E180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" t="n">
-        <v>12857</v>
+        <v>155</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5481,17 +5481,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>7.57</v>
+        <v>3.66</v>
       </c>
       <c r="E181" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>732</v>
+        <v>340</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5509,17 +5509,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>12.04</v>
+        <v>19.53</v>
       </c>
       <c r="E182" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F182" t="n">
-        <v>1024</v>
+        <v>382</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5537,23 +5537,23 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>60.86</v>
+        <v>633.1800000000001</v>
       </c>
       <c r="E183" t="n">
-        <v>20</v>
+        <v>205</v>
       </c>
       <c r="F183" t="n">
-        <v>4687</v>
+        <v>42492</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1694.07</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -5565,23 +5565,23 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>10.33</v>
+        <v>1325.98</v>
       </c>
       <c r="E184" t="n">
-        <v>4</v>
+        <v>422</v>
       </c>
       <c r="F184" t="n">
-        <v>519</v>
+        <v>50088</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>10627.14</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185">
@@ -5593,17 +5593,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3.67</v>
+        <v>1.29</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>193</v>
+        <v>747</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DJFH4K8B</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.66</v>
+        <v>43.94</v>
       </c>
       <c r="E186" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F186" t="n">
-        <v>373</v>
+        <v>3647</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5649,17 +5649,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>19.53</v>
+        <v>4.12</v>
       </c>
       <c r="E187" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>413</v>
+        <v>1172</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5677,23 +5677,23 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>726.33</v>
+        <v>103.05</v>
       </c>
       <c r="E188" t="n">
-        <v>241</v>
+        <v>33</v>
       </c>
       <c r="F188" t="n">
-        <v>48480</v>
+        <v>11410</v>
       </c>
       <c r="G188" t="n">
-        <v>1694.07</v>
+        <v>3048.3</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="189">
@@ -5705,23 +5705,23 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1532.04</v>
+        <v>17.99</v>
       </c>
       <c r="E189" t="n">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="F189" t="n">
-        <v>55730</v>
+        <v>2915</v>
       </c>
       <c r="G189" t="n">
-        <v>10627.14</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -5733,17 +5733,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>4.29</v>
+        <v>43.41</v>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="F190" t="n">
-        <v>848</v>
+        <v>1637</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5761,17 +5761,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>B0DJFH4K8B</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>53.5</v>
+        <v>2.3</v>
       </c>
       <c r="E191" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>4186</v>
+        <v>132</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5789,17 +5789,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DNJP9T35</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>1270</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5817,23 +5817,23 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>117.38</v>
+        <v>7.34</v>
       </c>
       <c r="E193" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F193" t="n">
-        <v>14317</v>
+        <v>741</v>
       </c>
       <c r="G193" t="n">
-        <v>3048.3</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>20.74</v>
+        <v>3.39</v>
       </c>
       <c r="E194" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>3188</v>
+        <v>588</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5873,23 +5873,23 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>49.59</v>
+        <v>58.64</v>
       </c>
       <c r="E195" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F195" t="n">
-        <v>1761</v>
+        <v>3833</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>3558.47</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -5901,17 +5901,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5929,17 +5929,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>B0DNJP9T35</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F197" t="n">
-        <v>2</v>
+        <v>3939</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5957,17 +5957,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>7.34</v>
+        <v>19.58</v>
       </c>
       <c r="E198" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F198" t="n">
-        <v>872</v>
+        <v>162</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5985,17 +5985,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>3.39</v>
+        <v>14.24</v>
       </c>
       <c r="E199" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F199" t="n">
-        <v>679</v>
+        <v>138</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -6013,23 +6013,23 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>73.62</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>4414</v>
+        <v>655</v>
       </c>
       <c r="G200" t="n">
-        <v>3558.47</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -6041,17 +6041,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F201" t="n">
-        <v>8</v>
+        <v>449</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -6069,23 +6069,23 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>7.97</v>
+        <v>3.64</v>
       </c>
       <c r="E202" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
-        <v>4742</v>
+        <v>494</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>571.1799999999999</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>177</v>
+        <v>273</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -6125,17 +6125,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>14.24</v>
+        <v>14.25</v>
       </c>
       <c r="E204" t="n">
         <v>4</v>
       </c>
       <c r="F204" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -6153,17 +6153,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F205" t="n">
-        <v>1117</v>
+        <v>645</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -6181,17 +6181,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F678RRCX</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>8.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>503</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -6209,23 +6209,23 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>3.64</v>
+        <v>12.34</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F207" t="n">
-        <v>570</v>
+        <v>138</v>
       </c>
       <c r="G207" t="n">
-        <v>571.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -6237,17 +6237,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>22.26</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F208" t="n">
-        <v>321</v>
+        <v>2353</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -6265,17 +6265,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0F67BW7SF</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>14.25</v>
+        <v>6.390000000000001</v>
       </c>
       <c r="E209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F209" t="n">
-        <v>126</v>
+        <v>1409</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -6293,17 +6293,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>6.35</v>
+        <v>2.84</v>
       </c>
       <c r="E210" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>696</v>
+        <v>747</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -6321,17 +6321,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>B0F678RRCX</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>16.8</v>
+        <v>22.74</v>
       </c>
       <c r="E211" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F211" t="n">
-        <v>151</v>
+        <v>2453</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -6349,17 +6349,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>12.34</v>
+        <v>3</v>
       </c>
       <c r="E212" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>152</v>
+        <v>842</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -6377,17 +6377,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>41.57</v>
+        <v>3.67</v>
       </c>
       <c r="E213" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>3260</v>
+        <v>615</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -6405,17 +6405,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>B0F67BW7SF</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>6.390000000000001</v>
+        <v>10.74</v>
       </c>
       <c r="E214" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F214" t="n">
-        <v>1551</v>
+        <v>652</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6433,17 +6433,17 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>5.84</v>
+        <v>93.86</v>
       </c>
       <c r="E215" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F215" t="n">
-        <v>864</v>
+        <v>2273</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6456,22 +6456,22 @@
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0CQX9ZZMH</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>22.74</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>2730</v>
+        <v>2</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6484,22 +6484,22 @@
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0CW1JJP9S</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>7.12</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>957</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6512,22 +6512,22 @@
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>700</v>
+        <v>6</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6540,22 +6540,22 @@
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>13.74</v>
+        <v>4.8</v>
       </c>
       <c r="E219" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>1060</v>
+        <v>64</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6568,22 +6568,22 @@
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-AT</t>
+          <t>Nexlev-Defensive-AT</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0D2LKB4BJ</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>100.79</v>
+        <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>2349</v>
+        <v>54</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>B0CQX9ZZMH</t>
+          <t>B0D81DLSFT</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>B0CW1JJP9S</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -6639,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6685,17 +6685,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D86Y2V7V</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>B0D2LKB4BJ</t>
+          <t>B0D86ZC9YT</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="F225" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>B0D81DLSFT</t>
+          <t>B0D9KCNVNM</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -6751,7 +6751,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D9KFQG8Q</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>B0D86Y2V7V</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -6835,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>B0D86ZC9YT</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -6863,7 +6863,7 @@
         <v>0</v>
       </c>
       <c r="F230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>B0D9KCNVNM</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -6891,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6937,17 +6937,17 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>B0D9KFQG8Q</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>25.8</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>257</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6965,7 +6965,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="F234" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6993,17 +6993,17 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DK9LYT4P</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -7059,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>185</v>
+        <v>12</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -7077,17 +7077,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DNJJKBKG</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>25.8</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>258</v>
+        <v>2</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DT6Y7KJM</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -7115,7 +7115,7 @@
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -7133,17 +7133,17 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>B0DK9LYT4P</t>
+          <t>B0DV9CY3XR</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
         <v>1</v>
-      </c>
-      <c r="F240" t="n">
-        <v>4</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -7171,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="D242" t="n">
@@ -7199,7 +7199,7 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>B0DNJJKBKG</t>
+          <t>B0DVSZ2VVJ</t>
         </is>
       </c>
       <c r="D243" t="n">
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>B0DT6Y7KJM</t>
+          <t>B0F29SZCVF</t>
         </is>
       </c>
       <c r="D244" t="n">
@@ -7255,7 +7255,7 @@
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>B0DV9CY3XR</t>
+          <t>B0F2MZ8CG9</t>
         </is>
       </c>
       <c r="D245" t="n">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0F2N11VTN</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0F2N1HTBT</t>
         </is>
       </c>
       <c r="D247" t="n">
@@ -7339,7 +7339,7 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0F2N37819</t>
         </is>
       </c>
       <c r="D248" t="n">
@@ -7367,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>B0F29SZCVF</t>
+          <t>B0F2N4N83Y</t>
         </is>
       </c>
       <c r="D249" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>B0F2MZ8CG9</t>
+          <t>B0F678L8YT</t>
         </is>
       </c>
       <c r="D250" t="n">
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>B0F2N11VTN</t>
+          <t>B0F679QJH4</t>
         </is>
       </c>
       <c r="D251" t="n">
@@ -7451,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="F251" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>B0F2N1HTBT</t>
+          <t>B0F67BSF2R</t>
         </is>
       </c>
       <c r="D252" t="n">
@@ -7479,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>B0F2N37819</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="D253" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>B0F2N4N83Y</t>
+          <t>B0FMF1D9NV</t>
         </is>
       </c>
       <c r="D254" t="n">
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G254" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>B0F678L8YT</t>
+          <t>B0FS7T8151</t>
         </is>
       </c>
       <c r="D255" t="n">
@@ -7563,7 +7563,7 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>B0F679QJH4</t>
+          <t>B0FYNKYJFN</t>
         </is>
       </c>
       <c r="D256" t="n">
@@ -7591,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -7609,17 +7609,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>B0F67BSF2R</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F257" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
@@ -7632,50 +7632,50 @@
       <c r="A258" t="inlineStr"/>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0</v>
+        <v>5523.98</v>
       </c>
       <c r="E258" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="F258" t="n">
-        <v>7</v>
+        <v>46162</v>
       </c>
       <c r="G258" t="n">
-        <v>0</v>
+        <v>12708.47</v>
       </c>
       <c r="H258" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>B0FMF1D9NV</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>2</v>
+        <v>134</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -7688,22 +7688,22 @@
       <c r="A260" t="inlineStr"/>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>B0FS7T8151</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>129.39</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -7716,50 +7716,50 @@
       <c r="A261" t="inlineStr"/>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>B0FYNKYJFN</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>63.93</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F261" t="n">
-        <v>3</v>
+        <v>326</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>2880.51</v>
       </c>
       <c r="H261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Nexlev-Defensive-AT</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>4.8</v>
+        <v>1031.47</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="F262" t="n">
-        <v>17</v>
+        <v>3399</v>
       </c>
       <c r="G262" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
       <c r="A263" t="inlineStr"/>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Nexlev-Multi Ad Group-Steam Cleaner -SP-KT -Exact/Phrase/Broad</t>
+          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7781,41 +7781,41 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>6737.34</v>
+        <v>21.43</v>
       </c>
       <c r="E263" t="n">
-        <v>356</v>
+        <v>3</v>
       </c>
       <c r="F263" t="n">
-        <v>51246</v>
+        <v>123</v>
       </c>
       <c r="G263" t="n">
-        <v>12708.47</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Nexlev-SP- B0GN8WW6BC - Stand Mixer with Stainless Steel Bowl - BM</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>4.48</v>
+        <v>169.54</v>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F264" t="n">
-        <v>141</v>
+        <v>3018</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -7828,22 +7828,22 @@
       <c r="A265" t="inlineStr"/>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>129.39</v>
+        <v>61.03</v>
       </c>
       <c r="E265" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F265" t="n">
-        <v>257</v>
+        <v>1739</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
@@ -7856,50 +7856,50 @@
       <c r="A266" t="inlineStr"/>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)</t>
+          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>63.93</v>
+        <v>154.17</v>
       </c>
       <c r="E266" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F266" t="n">
-        <v>326</v>
+        <v>1366</v>
       </c>
       <c r="G266" t="n">
-        <v>2880.51</v>
+        <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr"/>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-BM-SP</t>
+          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1283.67</v>
+        <v>1753</v>
       </c>
       <c r="E267" t="n">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="F267" t="n">
-        <v>3608</v>
+        <v>27876</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -7912,277 +7912,277 @@
       <c r="A268" t="inlineStr"/>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Nexlev-steam Cleaner For Home-B0CDPP45BM-Exact-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>21.43</v>
+        <v>814.17</v>
       </c>
       <c r="E268" t="n">
+        <v>146</v>
+      </c>
+      <c r="F268" t="n">
+        <v>24880</v>
+      </c>
+      <c r="G268" t="n">
+        <v>5336.45</v>
+      </c>
+      <c r="H268" t="n">
         <v>3</v>
-      </c>
-      <c r="F268" t="n">
-        <v>128</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr"/>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT(2)-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>256.25</v>
+        <v>1636.15</v>
       </c>
       <c r="E269" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
       <c r="F269" t="n">
-        <v>4228</v>
+        <v>14504</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>1778.82</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Nexliv- NexLev Hair Straightener Brush-B0D9KFP4MG-PT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>70.36</v>
+        <v>1968.82</v>
       </c>
       <c r="E270" t="n">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="F270" t="n">
-        <v>2361</v>
+        <v>7325</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>7115.25</v>
       </c>
       <c r="H270" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr"/>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Nexliv- Steam Mop-B0D2LJSQXZ-AT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>154.17</v>
+        <v>1904.89</v>
       </c>
       <c r="E271" t="n">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="F271" t="n">
-        <v>1366</v>
+        <v>15171</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>10420.33</v>
       </c>
       <c r="H271" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr"/>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nexliv--Steam Cleaner--B0F43P6D23-AT-SP</t>
+          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2093.83</v>
+        <v>744.4300000000001</v>
       </c>
       <c r="E272" t="n">
-        <v>203</v>
+        <v>63</v>
       </c>
       <c r="F272" t="n">
-        <v>31827</v>
+        <v>38050</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1778.82</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr"/>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-AT</t>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>814.17</v>
+        <v>163.47</v>
       </c>
       <c r="E273" t="n">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="F273" t="n">
-        <v>24891</v>
+        <v>769</v>
       </c>
       <c r="G273" t="n">
-        <v>5336.45</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr"/>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-BM-SP</t>
+          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-Phrase-SP</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>2034.65</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>16894</v>
+        <v>70</v>
       </c>
       <c r="G274" t="n">
-        <v>1778.82</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr"/>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT(2)-SP</t>
+          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>2351.04</v>
+        <v>22.77</v>
       </c>
       <c r="E275" t="n">
-        <v>127</v>
+        <v>2</v>
       </c>
       <c r="F275" t="n">
-        <v>9216</v>
+        <v>379</v>
       </c>
       <c r="G275" t="n">
-        <v>7115.25</v>
+        <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr"/>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-PT-SP</t>
+          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>2145.98</v>
+        <v>3034.72</v>
       </c>
       <c r="E276" t="n">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="F276" t="n">
-        <v>16034</v>
+        <v>89348</v>
       </c>
       <c r="G276" t="n">
-        <v>10420.33</v>
+        <v>3388.14</v>
       </c>
       <c r="H276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr"/>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nexliv-2 in 1 Stick Vacuum Cleaner-B0DCGHVN81-Phrase-SP(2)</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>804.47</v>
+        <v>2071.33</v>
       </c>
       <c r="E277" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F277" t="n">
-        <v>39154</v>
+        <v>25950</v>
       </c>
       <c r="G277" t="n">
-        <v>1778.82</v>
+        <v>1694.07</v>
       </c>
       <c r="H277" t="n">
         <v>1</v>
@@ -8192,22 +8192,22 @@
       <c r="A278" t="inlineStr"/>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-AT-SP</t>
+          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>163.47</v>
+        <v>951.48</v>
       </c>
       <c r="E278" t="n">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F278" t="n">
-        <v>769</v>
+        <v>20746</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -8220,249 +8220,249 @@
       <c r="A279" t="inlineStr"/>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nexliv-B0D9KDQCCM-Portable Sewing Machine-Phrase-SP</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>1055.08</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="F279" t="n">
-        <v>70</v>
+        <v>37094</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>12454.23</v>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr"/>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Nexliv-B0DCK4DR1B-Skin Lift Device-PT-SP</t>
+          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>22.77</v>
+        <v>21.5</v>
       </c>
       <c r="E280" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F280" t="n">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
+        <v>5083.06</v>
       </c>
       <c r="H280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr"/>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Nexliv-Electric Food Kettle-B0DFCG2VGS-BM-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>3531.68</v>
+        <v>969.78</v>
       </c>
       <c r="E281" t="n">
-        <v>382</v>
+        <v>68</v>
       </c>
       <c r="F281" t="n">
-        <v>106429</v>
+        <v>19148</v>
       </c>
       <c r="G281" t="n">
-        <v>5082.2</v>
+        <v>2033.05</v>
       </c>
       <c r="H281" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr"/>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-BM-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>2335.83</v>
+        <v>1411.55</v>
       </c>
       <c r="E282" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="F282" t="n">
-        <v>28794</v>
+        <v>18840</v>
       </c>
       <c r="G282" t="n">
-        <v>3388.14</v>
+        <v>2033.05</v>
       </c>
       <c r="H282" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr"/>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Nexliv-Handheld Steamer-B0D383WQPB-CT</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>951.48</v>
+        <v>2577.32</v>
       </c>
       <c r="E283" t="n">
-        <v>54</v>
+        <v>164</v>
       </c>
       <c r="F283" t="n">
-        <v>20747</v>
+        <v>44888</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>14211.03</v>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr"/>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-AT-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B08L46ZKKZ</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1175.23</v>
+        <v>2634.95</v>
       </c>
       <c r="E284" t="n">
-        <v>376</v>
+        <v>203</v>
       </c>
       <c r="F284" t="n">
-        <v>44074</v>
+        <v>10064</v>
       </c>
       <c r="G284" t="n">
-        <v>14995.76</v>
+        <v>23950.45</v>
       </c>
       <c r="H284" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr"/>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Nexliv-Mattress Sofa-B0CYSLCRQS-Exact-SP</t>
+          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0FNQS4RRD</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>21.5</v>
+        <v>211.92</v>
       </c>
       <c r="E285" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F285" t="n">
-        <v>409</v>
+        <v>5243</v>
       </c>
       <c r="G285" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr"/>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-BM</t>
+          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>969.78</v>
+        <v>10.4</v>
       </c>
       <c r="E286" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
-        <v>19148</v>
+        <v>47</v>
       </c>
       <c r="G286" t="n">
-        <v>2033.05</v>
+        <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr"/>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-CT</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1411.55</v>
+        <v>478.88</v>
       </c>
       <c r="E287" t="n">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="F287" t="n">
-        <v>18841</v>
+        <v>6138</v>
       </c>
       <c r="G287" t="n">
-        <v>2033.05</v>
+        <v>5083.9</v>
       </c>
       <c r="H287" t="n">
         <v>1</v>
@@ -8472,106 +8472,106 @@
       <c r="A288" t="inlineStr"/>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT(2)-SP</t>
+          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>2688.64</v>
+        <v>14.93</v>
       </c>
       <c r="E288" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>46605</v>
+        <v>413</v>
       </c>
       <c r="G288" t="n">
-        <v>14211.03</v>
+        <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr"/>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>B08L46ZKKZ</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>2893.24</v>
+        <v>420.48</v>
       </c>
       <c r="E289" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="F289" t="n">
-        <v>10576</v>
+        <v>6020</v>
       </c>
       <c r="G289" t="n">
-        <v>23950.45</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr"/>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Blender-B0FS6TB7CP-PT-SP</t>
+          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>B0FNQS4RRD</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>221.03</v>
+        <v>2504.26</v>
       </c>
       <c r="E290" t="n">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="F290" t="n">
-        <v>5597</v>
+        <v>11180</v>
       </c>
       <c r="G290" t="n">
-        <v>5083.9</v>
+        <v>5591.52</v>
       </c>
       <c r="H290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr"/>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Nexliv-Portable Sewing Machine-B0D9KDQCCM-Phrase-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="E291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F291" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
@@ -8584,25 +8584,25 @@
       <c r="A292" t="inlineStr"/>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-BM-SP</t>
+          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>478.88</v>
+        <v>672.8099999999999</v>
       </c>
       <c r="E292" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F292" t="n">
-        <v>6300</v>
+        <v>1982</v>
       </c>
       <c r="G292" t="n">
-        <v>5083.9</v>
+        <v>2668.64</v>
       </c>
       <c r="H292" t="n">
         <v>1</v>
@@ -8612,22 +8612,22 @@
       <c r="A293" t="inlineStr"/>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Nexliv-Stand Mixer-B0DVC7VJP1-CT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>14.93</v>
+        <v>1197.54</v>
       </c>
       <c r="E293" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="F293" t="n">
-        <v>457</v>
+        <v>12577</v>
       </c>
       <c r="G293" t="n">
         <v>0</v>
@@ -8640,63 +8640,63 @@
       <c r="A294" t="inlineStr"/>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner,B0F43P6D23-KW-SP-Exact</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>612.2</v>
+        <v>575.8200000000001</v>
       </c>
       <c r="E294" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F294" t="n">
-        <v>8614</v>
+        <v>2674</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>5083.9</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr"/>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner---B0F43P6D23-PT-SP</t>
+          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>3115.27</v>
+        <v>1923.34</v>
       </c>
       <c r="E295" t="n">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="F295" t="n">
-        <v>11836</v>
+        <v>15319</v>
       </c>
       <c r="G295" t="n">
-        <v>10928.8</v>
+        <v>5083.9</v>
       </c>
       <c r="H295" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr"/>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-AT-SP</t>
+          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8705,13 +8705,13 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>83.11</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -8724,78 +8724,78 @@
       <c r="A297" t="inlineStr"/>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-BM-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>824.41</v>
+        <v>1663.43</v>
       </c>
       <c r="E297" t="n">
-        <v>68</v>
+        <v>161</v>
       </c>
       <c r="F297" t="n">
-        <v>2232</v>
+        <v>30128</v>
       </c>
       <c r="G297" t="n">
-        <v>8005.92</v>
+        <v>0</v>
       </c>
       <c r="H297" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr"/>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Cleaner-B0F43P6D23-KW(2)-BM-SP</t>
+          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>2143.09</v>
       </c>
       <c r="E298" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="F298" t="n">
-        <v>0</v>
+        <v>64651</v>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
+        <v>3304.24</v>
       </c>
       <c r="H298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr"/>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-BM-and exact-SP</t>
+          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>1292.43</v>
+        <v>0</v>
       </c>
       <c r="E299" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F299" t="n">
-        <v>13336</v>
+        <v>33</v>
       </c>
       <c r="G299" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
       <c r="A300" t="inlineStr"/>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-CT-SP</t>
+          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -8817,69 +8817,69 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>575.8200000000001</v>
+        <v>518.53</v>
       </c>
       <c r="E300" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F300" t="n">
-        <v>2695</v>
+        <v>2874</v>
       </c>
       <c r="G300" t="n">
-        <v>5083.9</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr"/>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Nexliv-Steam Mop Floor Cleaner-B0DNJS23HS-Exact</t>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>2091.94</v>
+        <v>305.37</v>
       </c>
       <c r="E301" t="n">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="F301" t="n">
-        <v>16656</v>
+        <v>5524</v>
       </c>
       <c r="G301" t="n">
-        <v>5083.9</v>
+        <v>5422.030000000001</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Nexliv/Steam Cleaner-B0F43P6D23-Exact(1)-SP</t>
+          <t>Skadio B0BPPNQYX4-AT</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0BPPNQYX4</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>102.12</v>
+        <v>0</v>
       </c>
       <c r="E302" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -8892,22 +8892,22 @@
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-Exact-SP</t>
+          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1912.87</v>
+        <v>663.52</v>
       </c>
       <c r="E303" t="n">
-        <v>184</v>
+        <v>16</v>
       </c>
       <c r="F303" t="n">
-        <v>34234</v>
+        <v>9603</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
@@ -8920,195 +8920,27 @@
       <c r="A304" t="inlineStr"/>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Nexlive-Cordless Spin Mop-B0GKNGWLJ2-PT-SP</t>
+          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>2353.31</v>
+        <v>1297.68</v>
       </c>
       <c r="E304" t="n">
-        <v>225</v>
+        <v>78</v>
       </c>
       <c r="F304" t="n">
-        <v>68973</v>
+        <v>16947</v>
       </c>
       <c r="G304" t="n">
-        <v>3304.24</v>
+        <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr"/>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Nexlive-Oil Applicator Comb-B0DKK15YNJ-PH-SP</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>B0DKK15YNJ</t>
-        </is>
-      </c>
-      <c r="D305" t="n">
-        <v>0</v>
-      </c>
-      <c r="E305" t="n">
-        <v>0</v>
-      </c>
-      <c r="F305" t="n">
-        <v>33</v>
-      </c>
-      <c r="G305" t="n">
-        <v>0</v>
-      </c>
-      <c r="H305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr"/>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Nexlive-Steam Mop Flor Cleaner-B0DNJS23HS-PT/-SP</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>B0DNJS23HS</t>
-        </is>
-      </c>
-      <c r="D306" t="n">
-        <v>754.73</v>
-      </c>
-      <c r="E306" t="n">
-        <v>41</v>
-      </c>
-      <c r="F306" t="n">
-        <v>3019</v>
-      </c>
-      <c r="G306" t="n">
-        <v>0</v>
-      </c>
-      <c r="H306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr"/>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-Exact</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D307" t="n">
-        <v>305.37</v>
-      </c>
-      <c r="E307" t="n">
-        <v>31</v>
-      </c>
-      <c r="F307" t="n">
-        <v>5526</v>
-      </c>
-      <c r="G307" t="n">
-        <v>5422.030000000001</v>
-      </c>
-      <c r="H307" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr"/>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Skadio B0BPPNQYX4-AT</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>B0BPPNQYX4</t>
-        </is>
-      </c>
-      <c r="D308" t="n">
-        <v>0</v>
-      </c>
-      <c r="E308" t="n">
-        <v>0</v>
-      </c>
-      <c r="F308" t="n">
-        <v>132</v>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr"/>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>nexliv-B0FS6TB7CP Portable Blender-Exact-SP</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>B0FS6TB7CP</t>
-        </is>
-      </c>
-      <c r="D309" t="n">
-        <v>736.3100000000001</v>
-      </c>
-      <c r="E309" t="n">
-        <v>19</v>
-      </c>
-      <c r="F309" t="n">
-        <v>10663</v>
-      </c>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
-      <c r="H309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr"/>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>nexliv-Mattress Sofa Carpet B0DCK7ZH5P-Phrase-SP</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>B0DCK7ZH5P</t>
-        </is>
-      </c>
-      <c r="D310" t="n">
-        <v>1552.31</v>
-      </c>
-      <c r="E310" t="n">
-        <v>93</v>
-      </c>
-      <c r="F310" t="n">
-        <v>20336</v>
-      </c>
-      <c r="G310" t="n">
-        <v>0</v>
-      </c>
-      <c r="H310" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10329,13 +10161,13 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>808.97</v>
+        <v>726.84</v>
       </c>
       <c r="E43" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F43" t="n">
-        <v>5597</v>
+        <v>4712</v>
       </c>
       <c r="G43" t="n">
         <v>5083.9</v>
@@ -10357,13 +10189,13 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>705.84</v>
+        <v>552.03</v>
       </c>
       <c r="E44" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F44" t="n">
-        <v>14135</v>
+        <v>11103</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -10559,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>116</v>
+        <v>95</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -10587,7 +10419,7 @@
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>712</v>
+        <v>604</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -10615,7 +10447,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -10643,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>879</v>
+        <v>865</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -10691,7 +10523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10754,19 +10586,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11454</v>
+        <v>8200</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>2543.753333333334</v>
+        <v>1723.712262266036</v>
       </c>
       <c r="G2" t="n">
-        <v>7568.639999999999</v>
+        <v>4597.638987377277</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -10787,16 +10619,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11454</v>
+        <v>10933</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>2543.753333333334</v>
+        <v>2298.412617307453</v>
       </c>
       <c r="G3" t="n">
-        <v>7568.639999999999</v>
+        <v>6130.530999716038</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -10820,19 +10652,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11454</v>
+        <v>12133</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>2543.753333333334</v>
+        <v>2823.725120426511</v>
       </c>
       <c r="G4" t="n">
-        <v>7568.639999999999</v>
+        <v>9309.110012906684</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -10853,19 +10685,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7163</v>
+        <v>10137</v>
       </c>
       <c r="E5" t="n">
-        <v>272</v>
+        <v>388</v>
       </c>
       <c r="F5" t="n">
-        <v>2339.92</v>
+        <v>3358.588375263974</v>
       </c>
       <c r="G5" t="n">
-        <v>24919.925</v>
+        <v>27668.4922176918</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10886,19 +10718,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7163</v>
+        <v>1879</v>
       </c>
       <c r="E6" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>2339.92</v>
+        <v>622.701624736026</v>
       </c>
       <c r="G6" t="n">
-        <v>24919.925</v>
+        <v>5129.897782308203</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -10919,19 +10751,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9048</v>
+        <v>24429</v>
       </c>
       <c r="E7" t="n">
-        <v>58</v>
+        <v>156</v>
       </c>
       <c r="F7" t="n">
-        <v>740.0266666666666</v>
+        <v>2016.14</v>
       </c>
       <c r="G7" t="n">
-        <v>1904.126666666667</v>
+        <v>5712.38</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -10943,28 +10775,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DVSZ2VVJ</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9048</v>
+        <v>30438</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>230</v>
       </c>
       <c r="F8" t="n">
-        <v>740.0266666666666</v>
+        <v>2983.45</v>
       </c>
       <c r="G8" t="n">
-        <v>1904.126666666667</v>
+        <v>3140</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -10976,28 +10808,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All-  Calf Massager -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0FPGDVVCX</t>
+          <t>B0CDPMX152</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9048</v>
+        <v>885</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>740.0266666666666</v>
+        <v>598.425</v>
       </c>
       <c r="G9" t="n">
-        <v>1904.126666666667</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -11009,28 +10841,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11405</v>
+        <v>885</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>1128.036666666667</v>
+        <v>598.425</v>
       </c>
       <c r="G10" t="n">
-        <v>1046.666666666667</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -11042,28 +10874,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11405</v>
+        <v>4731</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>1128.036666666667</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>1046.666666666667</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -11075,28 +10907,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11405</v>
+        <v>4731</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>1128.036666666667</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>1046.666666666667</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -11108,22 +10940,22 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0CDPMX152</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1098</v>
+        <v>4731</v>
       </c>
       <c r="E13" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>719.965</v>
+        <v>161.1566666666667</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -11141,28 +10973,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPMX152- Garment Steamer-SBV-KT-Phrase</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1098</v>
+        <v>22139</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="F14" t="n">
-        <v>719.965</v>
+        <v>4730.360000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>7371.18</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -11174,28 +11006,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4731</v>
+        <v>5915</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
-        <v>161.1566666666667</v>
+        <v>823.53</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4235.59</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -11207,22 +11039,22 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4731</v>
+        <v>645</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>161.1566666666667</v>
+        <v>119.7</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -11240,22 +11072,22 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Cleaning Machine-SB-PT</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4731</v>
+        <v>645</v>
       </c>
       <c r="E17" t="n">
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>161.1566666666667</v>
+        <v>119.7</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -11273,28 +11105,28 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37902</v>
+        <v>645</v>
       </c>
       <c r="E18" t="n">
-        <v>497</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>7560.96</v>
+        <v>119.7</v>
       </c>
       <c r="G18" t="n">
-        <v>23849.13</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -11306,7 +11138,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11315,19 +11147,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>645</v>
+        <v>2272</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F19" t="n">
-        <v>119.7</v>
+        <v>602.71</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2541.52</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -11339,28 +11171,28 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>645</v>
+        <v>574</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
-        <v>119.7</v>
+        <v>343.93</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -11372,28 +11204,28 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>645</v>
+        <v>8727</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>299</v>
       </c>
       <c r="F21" t="n">
-        <v>119.7</v>
+        <v>4427.91416556267</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>27901.20995238776</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -11405,28 +11237,28 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2272</v>
+        <v>4654</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>160</v>
       </c>
       <c r="F22" t="n">
-        <v>602.71</v>
+        <v>2361.205834437329</v>
       </c>
       <c r="G22" t="n">
-        <v>2541.52</v>
+        <v>14878.45004761225</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -11438,25 +11270,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>189.25</v>
+        <v>66.19</v>
       </c>
       <c r="G23" t="n">
-        <v>1190</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -11471,25 +11303,25 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexlev-B0DKK15YNJ- Oil Applicator-SBV-KT-Exact/Phrase</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="E24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>189.25</v>
+        <v>66.19</v>
       </c>
       <c r="G24" t="n">
-        <v>1190</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -11504,28 +11336,28 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Cleaner - SBV-KT-Exact</t>
+          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GKNGWLJ2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15793</v>
+        <v>354</v>
       </c>
       <c r="E25" t="n">
-        <v>546</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>8089.09</v>
+        <v>66.19</v>
       </c>
       <c r="G25" t="n">
-        <v>41516.11</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -11537,28 +11369,28 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>354</v>
+        <v>5114</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>66.19</v>
+        <v>252.22</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11570,28 +11402,28 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>354</v>
+        <v>5114</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>66.19</v>
+        <v>252.22</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11603,28 +11435,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0DNJS23HS-Steam Mop-SB-KT-BM</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0GKNGWLJ2</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>354</v>
+        <v>5114</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>66.19</v>
+        <v>252.22</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11636,7 +11468,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11645,19 +11477,19 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5114</v>
+        <v>4517</v>
       </c>
       <c r="E29" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>252.22</v>
+        <v>562.1272149901804</v>
       </c>
       <c r="G29" t="n">
-        <v>1185.593333333333</v>
+        <v>7855.450773773616</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -11669,28 +11501,28 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5114</v>
+        <v>3946</v>
       </c>
       <c r="E30" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>252.22</v>
+        <v>491.0368468018694</v>
       </c>
       <c r="G30" t="n">
-        <v>1185.593333333333</v>
+        <v>6861.99791666106</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11702,28 +11534,28 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5114</v>
+        <v>12462</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="F31" t="n">
-        <v>252.22</v>
+        <v>1550.793588708785</v>
       </c>
       <c r="G31" t="n">
-        <v>1185.593333333333</v>
+        <v>21671.57606236588</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11740,23 +11572,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9151</v>
+        <v>5062</v>
       </c>
       <c r="E32" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
-        <v>1211.986666666667</v>
+        <v>629.920861820878</v>
       </c>
       <c r="G32" t="n">
-        <v>15575.42666666667</v>
+        <v>8802.833574769014</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11773,23 +11605,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9151</v>
+        <v>882</v>
       </c>
       <c r="E33" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>1211.986666666667</v>
+        <v>109.8014876782868</v>
       </c>
       <c r="G33" t="n">
-        <v>15575.42666666667</v>
+        <v>1534.42167243043</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -11801,28 +11633,28 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>9151</v>
+        <v>10846</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>1211.986666666667</v>
+        <v>396.295</v>
       </c>
       <c r="G34" t="n">
-        <v>15575.42666666667</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -11839,17 +11671,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12198</v>
+        <v>10846</v>
       </c>
       <c r="E35" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>471.15</v>
+        <v>396.295</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -11867,28 +11699,28 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12198</v>
+        <v>1104</v>
       </c>
       <c r="E36" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>471.15</v>
+        <v>934.7929997709824</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>7625.420000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11905,20 +11737,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1165</v>
+        <v>736</v>
       </c>
       <c r="E37" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>986.7033333333334</v>
+        <v>623.2304753752182</v>
       </c>
       <c r="G37" t="n">
-        <v>8048.87</v>
+        <v>5083.9</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
@@ -11938,23 +11770,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1165</v>
+        <v>1655</v>
       </c>
       <c r="E38" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>986.7033333333334</v>
+        <v>1402.0865248538</v>
       </c>
       <c r="G38" t="n">
-        <v>8048.87</v>
+        <v>11437.29</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11966,28 +11798,28 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1165</v>
+        <v>27</v>
       </c>
       <c r="E39" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>986.7033333333334</v>
+        <v>31.9</v>
       </c>
       <c r="G39" t="n">
-        <v>8048.87</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -12004,7 +11836,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12037,7 +11869,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12065,22 +11897,22 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>27</v>
+        <v>1315</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F42" t="n">
-        <v>31.9</v>
+        <v>53.05666666666666</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -12103,7 +11935,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12136,7 +11968,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12155,39 +11987,6 @@
         <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1315</v>
-      </c>
-      <c r="E45" t="n">
-        <v>4</v>
-      </c>
-      <c r="F45" t="n">
-        <v>53.05666666666666</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
@@ -10523,7 +10523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11374,23 +11374,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5114</v>
+        <v>13043</v>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>252.22</v>
+        <v>643.292985708973</v>
       </c>
       <c r="G26" t="n">
-        <v>1185.593333333333</v>
+        <v>3023.883416210665</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11407,23 +11407,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5114</v>
+        <v>2299</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>252.22</v>
+        <v>113.3670142910269</v>
       </c>
       <c r="G27" t="n">
-        <v>1185.593333333333</v>
+        <v>532.8965837893358</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11435,28 +11435,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5114</v>
+        <v>4517</v>
       </c>
       <c r="E28" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>252.22</v>
+        <v>562.1272149901804</v>
       </c>
       <c r="G28" t="n">
-        <v>1185.593333333333</v>
+        <v>7855.450773773616</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11473,20 +11473,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4517</v>
+        <v>3946</v>
       </c>
       <c r="E29" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F29" t="n">
-        <v>562.1272149901804</v>
+        <v>491.0368468018694</v>
       </c>
       <c r="G29" t="n">
-        <v>7855.450773773616</v>
+        <v>6861.99791666106</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -11506,23 +11506,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3946</v>
+        <v>12462</v>
       </c>
       <c r="E30" t="n">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="F30" t="n">
-        <v>491.0368468018694</v>
+        <v>1550.793588708785</v>
       </c>
       <c r="G30" t="n">
-        <v>6861.99791666106</v>
+        <v>21671.57606236588</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11539,23 +11539,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12462</v>
+        <v>5062</v>
       </c>
       <c r="E31" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F31" t="n">
-        <v>1550.793588708785</v>
+        <v>629.920861820878</v>
       </c>
       <c r="G31" t="n">
-        <v>21671.57606236588</v>
+        <v>8802.833574769014</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11572,23 +11572,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5062</v>
+        <v>882</v>
       </c>
       <c r="E32" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="F32" t="n">
-        <v>629.920861820878</v>
+        <v>109.8014876782868</v>
       </c>
       <c r="G32" t="n">
-        <v>8802.833574769014</v>
+        <v>1534.42167243043</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11600,25 +11600,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>882</v>
+        <v>10846</v>
       </c>
       <c r="E33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>109.8014876782868</v>
+        <v>396.295</v>
       </c>
       <c r="G33" t="n">
-        <v>1534.42167243043</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -11666,28 +11666,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10846</v>
+        <v>1104</v>
       </c>
       <c r="E35" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>396.295</v>
+        <v>934.7929997709824</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>7625.420000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11704,23 +11704,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1104</v>
+        <v>736</v>
       </c>
       <c r="E36" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
-        <v>934.7929997709824</v>
+        <v>623.2304753752182</v>
       </c>
       <c r="G36" t="n">
-        <v>7625.420000000001</v>
+        <v>5083.9</v>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11737,23 +11737,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>736</v>
+        <v>1655</v>
       </c>
       <c r="E37" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="F37" t="n">
-        <v>623.2304753752182</v>
+        <v>1402.0865248538</v>
       </c>
       <c r="G37" t="n">
-        <v>5083.9</v>
+        <v>11437.29</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -11765,28 +11765,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1655</v>
+        <v>27</v>
       </c>
       <c r="E38" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>1402.0865248538</v>
+        <v>31.9</v>
       </c>
       <c r="G38" t="n">
-        <v>11437.29</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -11864,22 +11864,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>27</v>
+        <v>1315</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>31.9</v>
+        <v>53.05666666666666</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -11954,39 +11954,6 @@
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>B0DKJSCLBD</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1315</v>
-      </c>
-      <c r="E44" t="n">
-        <v>4</v>
-      </c>
-      <c r="F44" t="n">
-        <v>53.05666666666666</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>

--- a/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week22.xlsx
@@ -5575,7 +5575,7 @@
         <v>422</v>
       </c>
       <c r="F184" t="n">
-        <v>50088</v>
+        <v>50087</v>
       </c>
       <c r="G184" t="n">
         <v>10627.14</v>
@@ -10523,7 +10523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,10 +10694,10 @@
         <v>3358.588375263974</v>
       </c>
       <c r="G5" t="n">
-        <v>27668.4922176918</v>
+        <v>28792.47865913018</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>622.701624736026</v>
       </c>
       <c r="G6" t="n">
-        <v>5129.897782308203</v>
+        <v>5338.291340869821</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -11374,23 +11374,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13043</v>
+        <v>5114</v>
       </c>
       <c r="E26" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>643.292985708973</v>
+        <v>252.22</v>
       </c>
       <c r="G26" t="n">
-        <v>3023.883416210665</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -11407,23 +11407,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2299</v>
+        <v>5114</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>113.3670142910269</v>
+        <v>252.22</v>
       </c>
       <c r="G27" t="n">
-        <v>532.8965837893358</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -11435,28 +11435,28 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+          <t>Nexlev-B0F43P6D23-Steam Cleaner-SB-KT-Phrase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4517</v>
+        <v>5114</v>
       </c>
       <c r="E28" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
-        <v>562.1272149901804</v>
+        <v>252.22</v>
       </c>
       <c r="G28" t="n">
-        <v>7855.450773773616</v>
+        <v>1185.593333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -11473,20 +11473,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3946</v>
+        <v>4517</v>
       </c>
       <c r="E29" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>491.0368468018694</v>
+        <v>562.1272149901804</v>
       </c>
       <c r="G29" t="n">
-        <v>6861.99791666106</v>
+        <v>7855.450773773616</v>
       </c>
       <c r="H29" t="n">
         <v>2</v>
@@ -11506,23 +11506,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12462</v>
+        <v>3946</v>
       </c>
       <c r="E30" t="n">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="F30" t="n">
-        <v>1550.793588708785</v>
+        <v>491.0368468018694</v>
       </c>
       <c r="G30" t="n">
-        <v>21671.57606236588</v>
+        <v>6861.99791666106</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -11539,23 +11539,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5062</v>
+        <v>12462</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="F31" t="n">
-        <v>629.920861820878</v>
+        <v>1550.793588708785</v>
       </c>
       <c r="G31" t="n">
-        <v>8802.833574769014</v>
+        <v>21671.57606236588</v>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -11572,23 +11572,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>882</v>
+        <v>5062</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
-        <v>109.8014876782868</v>
+        <v>629.920861820878</v>
       </c>
       <c r="G32" t="n">
-        <v>1534.42167243043</v>
+        <v>8802.833574769014</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -11600,25 +11600,25 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10846</v>
+        <v>882</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>396.295</v>
+        <v>109.8014876782868</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1534.42167243043</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -11666,28 +11666,28 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+          <t>Nexlev-Catch All-Vacuum Cleaner-SB-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1104</v>
+        <v>10846</v>
       </c>
       <c r="E35" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>934.7929997709824</v>
+        <v>396.295</v>
       </c>
       <c r="G35" t="n">
-        <v>7625.420000000001</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -11704,23 +11704,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>736</v>
+        <v>1104</v>
       </c>
       <c r="E36" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>623.2304753752182</v>
+        <v>934.7929997709824</v>
       </c>
       <c r="G36" t="n">
-        <v>5083.9</v>
+        <v>7625.420000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -11737,23 +11737,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1655</v>
+        <v>736</v>
       </c>
       <c r="E37" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>1402.0865248538</v>
+        <v>623.2304753752182</v>
       </c>
       <c r="G37" t="n">
-        <v>11437.29</v>
+        <v>5083.9</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -11765,28 +11765,28 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nexlev-Steamers-Branded</t>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0CDPP45BM</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>1655</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="F38" t="n">
-        <v>31.9</v>
+        <v>1402.0865248538</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>11437.29</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0CDPP45BM</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -11864,22 +11864,22 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nexlev-Vacuum Cleaner-Branded</t>
+          <t>Nexlev-Steamers-Branded</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0CYSLCRQS</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1315</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>53.05666666666666</v>
+        <v>31.9</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0CYSLCRQS</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -11954,6 +11954,39 @@
         <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlev-Vacuum Cleaner-Branded</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0DKJSCLBD</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1315</v>
+      </c>
+      <c r="E44" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>53.05666666666666</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Nexlev</t>
         </is>
